--- a/Avwap_Tarama_190326.xlsx
+++ b/Avwap_Tarama_190326.xlsx
@@ -76,6 +76,9 @@
     <t>ADESE</t>
   </si>
   <si>
+    <t>ADGYO</t>
+  </si>
+  <si>
     <t>AEFES</t>
   </si>
   <si>
@@ -470,9 +473,6 @@
   </si>
   <si>
     <t>DESA</t>
-  </si>
-  <si>
-    <t>DESPC</t>
   </si>
   <si>
     <t>DEVA</t>
@@ -2512,37 +2512,37 @@
         <v>552</v>
       </c>
       <c r="C7">
-        <v>17.52</v>
+        <v>59</v>
       </c>
       <c r="D7">
-        <v>0.06</v>
+        <v>2.43</v>
       </c>
       <c r="E7">
-        <v>-45.71</v>
+        <v>-81.29000000000001</v>
       </c>
       <c r="F7">
-        <v>40.92</v>
+        <v>58.79</v>
       </c>
       <c r="G7">
-        <v>-0.1</v>
+        <v>0.98</v>
       </c>
       <c r="J7">
-        <v>17.75</v>
+        <v>55.45</v>
       </c>
       <c r="K7">
-        <v>18.19</v>
+        <v>56.11</v>
       </c>
       <c r="L7">
-        <v>19.26</v>
+        <v>56.34</v>
       </c>
       <c r="M7">
-        <v>17.34</v>
+        <v>55.81</v>
       </c>
       <c r="N7">
-        <v>18.05</v>
+        <v>56.79</v>
       </c>
       <c r="O7">
-        <v>18.5</v>
+        <v>54.66</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -2553,37 +2553,37 @@
         <v>552</v>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>17.52</v>
       </c>
       <c r="D8">
-        <v>2.29</v>
+        <v>0.06</v>
       </c>
       <c r="E8">
-        <v>-55.39</v>
+        <v>-45.71</v>
       </c>
       <c r="F8">
-        <v>67.59999999999999</v>
+        <v>40.92</v>
       </c>
       <c r="G8">
-        <v>0.17</v>
+        <v>-0.1</v>
       </c>
       <c r="J8">
-        <v>14.68</v>
+        <v>17.75</v>
       </c>
       <c r="K8">
-        <v>14.93</v>
+        <v>18.19</v>
       </c>
       <c r="L8">
-        <v>15.87</v>
+        <v>19.26</v>
       </c>
       <c r="M8">
-        <v>14.72</v>
+        <v>17.34</v>
       </c>
       <c r="N8">
-        <v>15.11</v>
+        <v>18.05</v>
       </c>
       <c r="O8">
-        <v>16.26</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -2594,43 +2594,37 @@
         <v>552</v>
       </c>
       <c r="C9">
-        <v>228.2</v>
+        <v>17</v>
       </c>
       <c r="D9">
-        <v>3.07</v>
+        <v>2.29</v>
       </c>
       <c r="E9">
-        <v>68.54000000000001</v>
+        <v>-55.39</v>
       </c>
       <c r="F9">
-        <v>51</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G9">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="H9" t="s">
-        <v>555</v>
-      </c>
-      <c r="I9" t="s">
-        <v>618</v>
+        <v>0.17</v>
       </c>
       <c r="J9">
-        <v>221.17</v>
+        <v>14.68</v>
       </c>
       <c r="K9">
-        <v>229.05</v>
+        <v>14.93</v>
       </c>
       <c r="L9">
-        <v>232.25</v>
+        <v>15.87</v>
       </c>
       <c r="M9">
-        <v>225.29</v>
+        <v>14.72</v>
       </c>
       <c r="N9">
-        <v>230.46</v>
+        <v>15.11</v>
       </c>
       <c r="O9">
-        <v>220.48</v>
+        <v>16.26</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -2641,37 +2635,43 @@
         <v>552</v>
       </c>
       <c r="C10">
-        <v>3.04</v>
+        <v>228.2</v>
       </c>
       <c r="D10">
-        <v>0.66</v>
+        <v>3.07</v>
       </c>
       <c r="E10">
-        <v>-52.5</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="F10">
-        <v>52.92</v>
+        <v>51</v>
       </c>
       <c r="G10">
-        <v>0.03</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="H10" t="s">
+        <v>555</v>
+      </c>
+      <c r="I10" t="s">
+        <v>618</v>
       </c>
       <c r="J10">
-        <v>3.23</v>
+        <v>221.17</v>
       </c>
       <c r="K10">
-        <v>3.18</v>
+        <v>229.05</v>
       </c>
       <c r="L10">
-        <v>2.96</v>
+        <v>232.25</v>
       </c>
       <c r="M10">
-        <v>3.22</v>
+        <v>225.29</v>
       </c>
       <c r="N10">
-        <v>3.08</v>
+        <v>230.46</v>
       </c>
       <c r="O10">
-        <v>2.9</v>
+        <v>220.48</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -2682,37 +2682,37 @@
         <v>552</v>
       </c>
       <c r="C11">
-        <v>21.88</v>
+        <v>3.04</v>
       </c>
       <c r="D11">
-        <v>-0.91</v>
+        <v>0.66</v>
       </c>
       <c r="E11">
-        <v>-71.40000000000001</v>
+        <v>-52.5</v>
       </c>
       <c r="F11">
-        <v>28.88</v>
+        <v>52.92</v>
       </c>
       <c r="G11">
-        <v>-0.24</v>
+        <v>0.03</v>
       </c>
       <c r="J11">
-        <v>24.9</v>
+        <v>3.23</v>
       </c>
       <c r="K11">
-        <v>24.73</v>
+        <v>3.18</v>
       </c>
       <c r="L11">
-        <v>24.95</v>
+        <v>2.96</v>
       </c>
       <c r="M11">
-        <v>25.13</v>
+        <v>3.22</v>
       </c>
       <c r="N11">
-        <v>24.83</v>
+        <v>3.08</v>
       </c>
       <c r="O11">
-        <v>24.71</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -2723,37 +2723,37 @@
         <v>552</v>
       </c>
       <c r="C12">
-        <v>20.48</v>
+        <v>21.88</v>
       </c>
       <c r="D12">
-        <v>-0.78</v>
+        <v>-0.91</v>
       </c>
       <c r="E12">
-        <v>-71.45999999999999</v>
+        <v>-71.40000000000001</v>
       </c>
       <c r="F12">
-        <v>48.17</v>
+        <v>28.88</v>
       </c>
       <c r="G12">
-        <v>0.08</v>
+        <v>-0.24</v>
       </c>
       <c r="J12">
-        <v>18.82</v>
+        <v>24.9</v>
       </c>
       <c r="K12">
-        <v>20.36</v>
+        <v>24.73</v>
       </c>
       <c r="L12">
-        <v>21.1</v>
+        <v>24.95</v>
       </c>
       <c r="M12">
-        <v>19.88</v>
+        <v>25.13</v>
       </c>
       <c r="N12">
-        <v>21.35</v>
+        <v>24.83</v>
       </c>
       <c r="O12">
-        <v>21.23</v>
+        <v>24.71</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -2764,43 +2764,37 @@
         <v>552</v>
       </c>
       <c r="C13">
-        <v>73.59999999999999</v>
+        <v>20.48</v>
       </c>
       <c r="D13">
-        <v>-2.77</v>
+        <v>-0.78</v>
       </c>
       <c r="E13">
-        <v>-58.13</v>
+        <v>-71.45999999999999</v>
       </c>
       <c r="F13">
-        <v>38.53</v>
+        <v>48.17</v>
       </c>
       <c r="G13">
-        <v>-0.73</v>
-      </c>
-      <c r="H13" t="s">
-        <v>556</v>
-      </c>
-      <c r="I13" t="s">
-        <v>616</v>
+        <v>0.08</v>
       </c>
       <c r="J13">
-        <v>73.76000000000001</v>
+        <v>18.82</v>
       </c>
       <c r="K13">
-        <v>81.34</v>
+        <v>20.36</v>
       </c>
       <c r="L13">
-        <v>83.95999999999999</v>
+        <v>21.1</v>
       </c>
       <c r="M13">
-        <v>72.87</v>
+        <v>19.88</v>
       </c>
       <c r="N13">
-        <v>76.34999999999999</v>
+        <v>21.35</v>
       </c>
       <c r="O13">
-        <v>81.70999999999999</v>
+        <v>21.23</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -2811,43 +2805,43 @@
         <v>552</v>
       </c>
       <c r="C14">
-        <v>199.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="D14">
-        <v>-1.09</v>
+        <v>-2.77</v>
       </c>
       <c r="E14">
-        <v>-37.37</v>
+        <v>-58.13</v>
       </c>
       <c r="F14">
-        <v>43.81</v>
+        <v>38.53</v>
       </c>
       <c r="G14">
-        <v>-2.19</v>
+        <v>-0.73</v>
       </c>
       <c r="H14" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="I14" t="s">
         <v>616</v>
       </c>
       <c r="J14">
-        <v>181.08</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="K14">
-        <v>195.99</v>
+        <v>81.34</v>
       </c>
       <c r="L14">
-        <v>211.64</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="M14">
-        <v>177.44</v>
+        <v>72.87</v>
       </c>
       <c r="N14">
-        <v>184.83</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="O14">
-        <v>200.44</v>
+        <v>81.70999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -2858,37 +2852,43 @@
         <v>552</v>
       </c>
       <c r="C15">
-        <v>9.699999999999999</v>
+        <v>199.2</v>
       </c>
       <c r="D15">
-        <v>0.31</v>
+        <v>-1.09</v>
       </c>
       <c r="E15">
-        <v>-51.2</v>
+        <v>-37.37</v>
       </c>
       <c r="F15">
-        <v>33.22</v>
+        <v>43.81</v>
       </c>
       <c r="G15">
-        <v>-0.03</v>
+        <v>-2.19</v>
+      </c>
+      <c r="H15" t="s">
+        <v>553</v>
+      </c>
+      <c r="I15" t="s">
+        <v>616</v>
       </c>
       <c r="J15">
-        <v>11.1</v>
+        <v>181.08</v>
       </c>
       <c r="K15">
-        <v>10.9</v>
+        <v>195.99</v>
       </c>
       <c r="L15">
-        <v>10.68</v>
+        <v>211.64</v>
       </c>
       <c r="M15">
-        <v>11.13</v>
+        <v>177.44</v>
       </c>
       <c r="N15">
-        <v>10.94</v>
+        <v>184.83</v>
       </c>
       <c r="O15">
-        <v>10.89</v>
+        <v>200.44</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -2899,37 +2899,37 @@
         <v>552</v>
       </c>
       <c r="C16">
-        <v>39.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D16">
-        <v>2.11</v>
+        <v>0.31</v>
       </c>
       <c r="E16">
-        <v>-50.14</v>
+        <v>-51.2</v>
       </c>
       <c r="F16">
-        <v>71.36</v>
+        <v>33.22</v>
       </c>
       <c r="G16">
-        <v>0.7</v>
+        <v>-0.03</v>
       </c>
       <c r="J16">
-        <v>28.53</v>
+        <v>11.1</v>
       </c>
       <c r="K16">
-        <v>29.32</v>
+        <v>10.9</v>
       </c>
       <c r="L16">
-        <v>31.12</v>
+        <v>10.68</v>
       </c>
       <c r="M16">
-        <v>29.19</v>
+        <v>11.13</v>
       </c>
       <c r="N16">
-        <v>29.67</v>
+        <v>10.94</v>
       </c>
       <c r="O16">
-        <v>31.47</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -2940,37 +2940,37 @@
         <v>552</v>
       </c>
       <c r="C17">
-        <v>22.2</v>
+        <v>39.7</v>
       </c>
       <c r="D17">
-        <v>1.56</v>
+        <v>2.11</v>
       </c>
       <c r="E17">
-        <v>-64.92</v>
+        <v>-50.14</v>
       </c>
       <c r="F17">
-        <v>68.69</v>
+        <v>71.36</v>
       </c>
       <c r="G17">
-        <v>0.33</v>
+        <v>0.7</v>
       </c>
       <c r="J17">
-        <v>19.2</v>
+        <v>28.53</v>
       </c>
       <c r="K17">
-        <v>19.37</v>
+        <v>29.32</v>
       </c>
       <c r="L17">
-        <v>19.63</v>
+        <v>31.12</v>
       </c>
       <c r="M17">
-        <v>19.27</v>
+        <v>29.19</v>
       </c>
       <c r="N17">
-        <v>19.49</v>
+        <v>29.67</v>
       </c>
       <c r="O17">
-        <v>19.96</v>
+        <v>31.47</v>
       </c>
     </row>
     <row r="18" spans="1:15">
@@ -2981,43 +2981,37 @@
         <v>552</v>
       </c>
       <c r="C18">
-        <v>8.029999999999999</v>
+        <v>22.2</v>
       </c>
       <c r="D18">
-        <v>1.13</v>
+        <v>1.56</v>
       </c>
       <c r="E18">
-        <v>-52.33</v>
+        <v>-64.92</v>
       </c>
       <c r="F18">
-        <v>54.29</v>
+        <v>68.69</v>
       </c>
       <c r="G18">
-        <v>0.06</v>
-      </c>
-      <c r="H18" t="s">
-        <v>557</v>
-      </c>
-      <c r="I18" t="s">
-        <v>618</v>
+        <v>0.33</v>
       </c>
       <c r="J18">
-        <v>7.54</v>
+        <v>19.2</v>
       </c>
       <c r="K18">
-        <v>7.85</v>
+        <v>19.37</v>
       </c>
       <c r="L18">
-        <v>8</v>
+        <v>19.63</v>
       </c>
       <c r="M18">
-        <v>7.76</v>
+        <v>19.27</v>
       </c>
       <c r="N18">
-        <v>7.9</v>
+        <v>19.49</v>
       </c>
       <c r="O18">
-        <v>7.66</v>
+        <v>19.96</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -3028,37 +3022,43 @@
         <v>552</v>
       </c>
       <c r="C19">
-        <v>11.1</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="D19">
-        <v>-0.09</v>
+        <v>1.13</v>
       </c>
       <c r="E19">
-        <v>-76.56999999999999</v>
+        <v>-52.33</v>
       </c>
       <c r="F19">
-        <v>62.14</v>
+        <v>54.29</v>
       </c>
       <c r="G19">
-        <v>0.12</v>
+        <v>0.06</v>
+      </c>
+      <c r="H19" t="s">
+        <v>557</v>
+      </c>
+      <c r="I19" t="s">
+        <v>618</v>
       </c>
       <c r="J19">
-        <v>10.82</v>
+        <v>7.54</v>
       </c>
       <c r="K19">
-        <v>10.78</v>
+        <v>7.85</v>
       </c>
       <c r="L19">
-        <v>10.73</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>10.82</v>
+        <v>7.76</v>
       </c>
       <c r="N19">
-        <v>10.73</v>
+        <v>7.9</v>
       </c>
       <c r="O19">
-        <v>10.44</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -3069,37 +3069,37 @@
         <v>552</v>
       </c>
       <c r="C20">
-        <v>77.95</v>
+        <v>11.1</v>
       </c>
       <c r="D20">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="E20">
-        <v>-48.57</v>
+        <v>-76.56999999999999</v>
       </c>
       <c r="F20">
-        <v>64.06</v>
+        <v>62.14</v>
       </c>
       <c r="G20">
-        <v>1.02</v>
+        <v>0.12</v>
       </c>
       <c r="J20">
-        <v>68.53</v>
+        <v>10.82</v>
       </c>
       <c r="K20">
-        <v>70.55</v>
+        <v>10.78</v>
       </c>
       <c r="L20">
-        <v>70.84999999999999</v>
+        <v>10.73</v>
       </c>
       <c r="M20">
-        <v>69.58</v>
+        <v>10.82</v>
       </c>
       <c r="N20">
-        <v>70.72</v>
+        <v>10.73</v>
       </c>
       <c r="O20">
-        <v>71.89</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="21" spans="1:15">
@@ -3110,37 +3110,37 @@
         <v>552</v>
       </c>
       <c r="C21">
-        <v>28.34</v>
+        <v>77.95</v>
       </c>
       <c r="D21">
-        <v>0.71</v>
+        <v>-0.06</v>
       </c>
       <c r="E21">
-        <v>-70.36</v>
+        <v>-48.57</v>
       </c>
       <c r="F21">
-        <v>65.23999999999999</v>
+        <v>64.06</v>
       </c>
       <c r="G21">
-        <v>0.08</v>
+        <v>1.02</v>
       </c>
       <c r="J21">
-        <v>24.45</v>
+        <v>68.53</v>
       </c>
       <c r="K21">
-        <v>24.99</v>
+        <v>70.55</v>
       </c>
       <c r="L21">
-        <v>25.39</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="M21">
-        <v>24.56</v>
+        <v>69.58</v>
       </c>
       <c r="N21">
-        <v>25.3</v>
+        <v>70.72</v>
       </c>
       <c r="O21">
-        <v>26.44</v>
+        <v>71.89</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -3151,43 +3151,37 @@
         <v>552</v>
       </c>
       <c r="C22">
-        <v>2.7</v>
+        <v>28.34</v>
       </c>
       <c r="D22">
-        <v>3.05</v>
+        <v>0.71</v>
       </c>
       <c r="E22">
-        <v>-63.11</v>
+        <v>-70.36</v>
       </c>
       <c r="F22">
-        <v>49.09</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22" t="s">
-        <v>558</v>
-      </c>
-      <c r="I22" t="s">
-        <v>618</v>
+        <v>0.08</v>
       </c>
       <c r="J22">
-        <v>2.83</v>
+        <v>24.45</v>
       </c>
       <c r="K22">
-        <v>2.83</v>
+        <v>24.99</v>
       </c>
       <c r="L22">
-        <v>2.83</v>
+        <v>25.39</v>
       </c>
       <c r="M22">
-        <v>2.83</v>
+        <v>24.56</v>
       </c>
       <c r="N22">
-        <v>2.84</v>
+        <v>25.3</v>
       </c>
       <c r="O22">
-        <v>2.65</v>
+        <v>26.44</v>
       </c>
     </row>
     <row r="23" spans="1:15">
@@ -3198,37 +3192,43 @@
         <v>552</v>
       </c>
       <c r="C23">
-        <v>89.7</v>
+        <v>2.7</v>
       </c>
       <c r="D23">
-        <v>-0.33</v>
+        <v>3.05</v>
       </c>
       <c r="E23">
-        <v>-24.85</v>
+        <v>-63.11</v>
       </c>
       <c r="F23">
-        <v>32.23</v>
+        <v>49.09</v>
       </c>
       <c r="G23">
-        <v>-0.61</v>
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
+        <v>558</v>
+      </c>
+      <c r="I23" t="s">
+        <v>618</v>
       </c>
       <c r="J23">
-        <v>105.27</v>
+        <v>2.83</v>
       </c>
       <c r="K23">
-        <v>105.9</v>
+        <v>2.83</v>
       </c>
       <c r="L23">
-        <v>101.02</v>
+        <v>2.83</v>
       </c>
       <c r="M23">
-        <v>104.58</v>
+        <v>2.83</v>
       </c>
       <c r="N23">
-        <v>105.86</v>
+        <v>2.84</v>
       </c>
       <c r="O23">
-        <v>105.17</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="24" spans="1:15">
@@ -3239,37 +3239,37 @@
         <v>552</v>
       </c>
       <c r="C24">
-        <v>8.119999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="D24">
-        <v>-1.34</v>
+        <v>-0.33</v>
       </c>
       <c r="E24">
-        <v>-37.53</v>
+        <v>-24.85</v>
       </c>
       <c r="F24">
-        <v>38.13</v>
+        <v>32.23</v>
       </c>
       <c r="G24">
-        <v>-0.05</v>
+        <v>-0.61</v>
       </c>
       <c r="J24">
-        <v>8.65</v>
+        <v>105.27</v>
       </c>
       <c r="K24">
-        <v>8.81</v>
+        <v>105.9</v>
       </c>
       <c r="L24">
-        <v>9.09</v>
+        <v>101.02</v>
       </c>
       <c r="M24">
-        <v>8.6</v>
+        <v>104.58</v>
       </c>
       <c r="N24">
-        <v>8.699999999999999</v>
+        <v>105.86</v>
       </c>
       <c r="O24">
-        <v>8.869999999999999</v>
+        <v>105.17</v>
       </c>
     </row>
     <row r="25" spans="1:15">
@@ -3280,37 +3280,37 @@
         <v>552</v>
       </c>
       <c r="C25">
-        <v>755</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="D25">
-        <v>-0.07000000000000001</v>
+        <v>-1.34</v>
       </c>
       <c r="E25">
-        <v>-76.55</v>
+        <v>-37.53</v>
       </c>
       <c r="F25">
-        <v>32.35</v>
+        <v>38.13</v>
       </c>
       <c r="G25">
-        <v>0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="J25">
-        <v>878.7</v>
+        <v>8.65</v>
       </c>
       <c r="K25">
-        <v>883.28</v>
+        <v>8.81</v>
       </c>
       <c r="L25">
-        <v>861.53</v>
+        <v>9.09</v>
       </c>
       <c r="M25">
-        <v>879.53</v>
+        <v>8.6</v>
       </c>
       <c r="N25">
-        <v>874.0700000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O25">
-        <v>762.1</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:15">
@@ -3321,43 +3321,37 @@
         <v>552</v>
       </c>
       <c r="C26">
-        <v>127.1</v>
+        <v>755</v>
       </c>
       <c r="D26">
-        <v>0.79</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E26">
-        <v>-47.92</v>
+        <v>-76.55</v>
       </c>
       <c r="F26">
-        <v>49.18</v>
+        <v>32.35</v>
       </c>
       <c r="G26">
-        <v>0.17</v>
-      </c>
-      <c r="H26" t="s">
-        <v>559</v>
-      </c>
-      <c r="I26" t="s">
-        <v>618</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J26">
-        <v>122.54</v>
+        <v>878.7</v>
       </c>
       <c r="K26">
-        <v>123.54</v>
+        <v>883.28</v>
       </c>
       <c r="L26">
-        <v>126.43</v>
+        <v>861.53</v>
       </c>
       <c r="M26">
-        <v>123.47</v>
+        <v>879.53</v>
       </c>
       <c r="N26">
-        <v>124.51</v>
+        <v>874.0700000000001</v>
       </c>
       <c r="O26">
-        <v>125.78</v>
+        <v>762.1</v>
       </c>
     </row>
     <row r="27" spans="1:15">
@@ -3368,37 +3362,43 @@
         <v>552</v>
       </c>
       <c r="C27">
-        <v>36.82</v>
+        <v>127.1</v>
       </c>
       <c r="D27">
-        <v>-2.33</v>
+        <v>0.79</v>
       </c>
       <c r="E27">
-        <v>30.44</v>
+        <v>-47.92</v>
       </c>
       <c r="F27">
-        <v>35.24</v>
+        <v>49.18</v>
       </c>
       <c r="G27">
-        <v>-0.03</v>
+        <v>0.17</v>
+      </c>
+      <c r="H27" t="s">
+        <v>559</v>
+      </c>
+      <c r="I27" t="s">
+        <v>618</v>
       </c>
       <c r="J27">
-        <v>41.58</v>
+        <v>122.54</v>
       </c>
       <c r="K27">
-        <v>41.22</v>
+        <v>123.54</v>
       </c>
       <c r="L27">
-        <v>41.16</v>
+        <v>126.43</v>
       </c>
       <c r="M27">
-        <v>41.84</v>
+        <v>123.47</v>
       </c>
       <c r="N27">
-        <v>41.34</v>
+        <v>124.51</v>
       </c>
       <c r="O27">
-        <v>41.13</v>
+        <v>125.78</v>
       </c>
     </row>
     <row r="28" spans="1:15">
@@ -3409,37 +3409,37 @@
         <v>552</v>
       </c>
       <c r="C28">
-        <v>11.28</v>
+        <v>36.82</v>
       </c>
       <c r="D28">
-        <v>-1.74</v>
+        <v>-2.33</v>
       </c>
       <c r="E28">
-        <v>-85.34</v>
+        <v>30.44</v>
       </c>
       <c r="F28">
-        <v>45.47</v>
+        <v>35.24</v>
       </c>
       <c r="G28">
-        <v>0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="J28">
-        <v>12.11</v>
+        <v>41.58</v>
       </c>
       <c r="K28">
-        <v>12.69</v>
+        <v>41.22</v>
       </c>
       <c r="L28">
-        <v>12.68</v>
+        <v>41.16</v>
       </c>
       <c r="M28">
-        <v>12.41</v>
+        <v>41.84</v>
       </c>
       <c r="N28">
-        <v>12.9</v>
+        <v>41.34</v>
       </c>
       <c r="O28">
-        <v>11.07</v>
+        <v>41.13</v>
       </c>
     </row>
     <row r="29" spans="1:15">
@@ -3450,43 +3450,37 @@
         <v>552</v>
       </c>
       <c r="C29">
-        <v>17.72</v>
+        <v>11.28</v>
       </c>
       <c r="D29">
-        <v>-2.96</v>
+        <v>-1.74</v>
       </c>
       <c r="E29">
-        <v>-52</v>
+        <v>-85.34</v>
       </c>
       <c r="F29">
-        <v>51.05</v>
+        <v>45.47</v>
       </c>
       <c r="G29">
-        <v>0.15</v>
-      </c>
-      <c r="H29" t="s">
-        <v>560</v>
-      </c>
-      <c r="I29" t="s">
-        <v>619</v>
+        <v>0.1</v>
       </c>
       <c r="J29">
-        <v>19.32</v>
+        <v>12.11</v>
       </c>
       <c r="K29">
-        <v>19.13</v>
+        <v>12.69</v>
       </c>
       <c r="L29">
-        <v>19</v>
+        <v>12.68</v>
       </c>
       <c r="M29">
-        <v>18.42</v>
+        <v>12.41</v>
       </c>
       <c r="N29">
-        <v>19.24</v>
+        <v>12.9</v>
       </c>
       <c r="O29">
-        <v>17.27</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="30" spans="1:15">
@@ -3497,37 +3491,43 @@
         <v>552</v>
       </c>
       <c r="C30">
-        <v>305</v>
+        <v>17.72</v>
       </c>
       <c r="D30">
-        <v>3.83</v>
+        <v>-2.96</v>
       </c>
       <c r="E30">
-        <v>6.54</v>
+        <v>-52</v>
       </c>
       <c r="F30">
-        <v>66.53</v>
+        <v>51.05</v>
       </c>
       <c r="G30">
-        <v>0.65</v>
+        <v>0.15</v>
+      </c>
+      <c r="H30" t="s">
+        <v>560</v>
+      </c>
+      <c r="I30" t="s">
+        <v>619</v>
       </c>
       <c r="J30">
-        <v>253.9</v>
+        <v>19.32</v>
       </c>
       <c r="K30">
-        <v>273.19</v>
+        <v>19.13</v>
       </c>
       <c r="L30">
-        <v>280.09</v>
+        <v>19</v>
       </c>
       <c r="M30">
-        <v>262.07</v>
+        <v>18.42</v>
       </c>
       <c r="N30">
-        <v>273.91</v>
+        <v>19.24</v>
       </c>
       <c r="O30">
-        <v>279.05</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="31" spans="1:15">
@@ -3538,37 +3538,37 @@
         <v>552</v>
       </c>
       <c r="C31">
-        <v>82.05</v>
+        <v>305</v>
       </c>
       <c r="D31">
-        <v>-0.89</v>
+        <v>3.83</v>
       </c>
       <c r="E31">
-        <v>-31.33</v>
+        <v>6.54</v>
       </c>
       <c r="F31">
-        <v>38.97</v>
+        <v>66.53</v>
       </c>
       <c r="G31">
-        <v>-0.74</v>
+        <v>0.65</v>
       </c>
       <c r="J31">
-        <v>87.58</v>
+        <v>253.9</v>
       </c>
       <c r="K31">
-        <v>87.81999999999999</v>
+        <v>273.19</v>
       </c>
       <c r="L31">
-        <v>88.03</v>
+        <v>280.09</v>
       </c>
       <c r="M31">
-        <v>85.79000000000001</v>
+        <v>262.07</v>
       </c>
       <c r="N31">
-        <v>88.58</v>
+        <v>273.91</v>
       </c>
       <c r="O31">
-        <v>86.54000000000001</v>
+        <v>279.05</v>
       </c>
     </row>
     <row r="32" spans="1:15">
@@ -3579,37 +3579,37 @@
         <v>552</v>
       </c>
       <c r="C32">
-        <v>15.1</v>
+        <v>82.05</v>
       </c>
       <c r="D32">
-        <v>0.4</v>
+        <v>-0.89</v>
       </c>
       <c r="E32">
-        <v>-71.78</v>
+        <v>-31.33</v>
       </c>
       <c r="F32">
-        <v>41.31</v>
+        <v>38.97</v>
       </c>
       <c r="G32">
-        <v>-0.13</v>
+        <v>-0.74</v>
       </c>
       <c r="J32">
-        <v>16.51</v>
+        <v>87.58</v>
       </c>
       <c r="K32">
-        <v>16.61</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="L32">
-        <v>16.58</v>
+        <v>88.03</v>
       </c>
       <c r="M32">
-        <v>16.32</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="N32">
-        <v>16.55</v>
+        <v>88.58</v>
       </c>
       <c r="O32">
-        <v>16.53</v>
+        <v>86.54000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:15">
@@ -3620,37 +3620,37 @@
         <v>552</v>
       </c>
       <c r="C33">
-        <v>2.98</v>
+        <v>15.1</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
       <c r="E33">
-        <v>-68.68000000000001</v>
+        <v>-71.78</v>
       </c>
       <c r="F33">
-        <v>37.3</v>
+        <v>41.31</v>
       </c>
       <c r="G33">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="J33">
-        <v>3.43</v>
+        <v>16.51</v>
       </c>
       <c r="K33">
-        <v>3.46</v>
+        <v>16.61</v>
       </c>
       <c r="L33">
-        <v>3.83</v>
+        <v>16.58</v>
       </c>
       <c r="M33">
-        <v>3.42</v>
+        <v>16.32</v>
       </c>
       <c r="N33">
-        <v>3.45</v>
+        <v>16.55</v>
       </c>
       <c r="O33">
-        <v>3.58</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="34" spans="1:15">
@@ -3661,37 +3661,37 @@
         <v>552</v>
       </c>
       <c r="C34">
-        <v>14.02</v>
+        <v>2.98</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E34">
-        <v>-60.75</v>
+        <v>-68.68000000000001</v>
       </c>
       <c r="F34">
-        <v>35.36</v>
+        <v>37.3</v>
       </c>
       <c r="G34">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="J34">
-        <v>16.35</v>
+        <v>3.43</v>
       </c>
       <c r="K34">
-        <v>16.43</v>
+        <v>3.46</v>
       </c>
       <c r="L34">
-        <v>15.58</v>
+        <v>3.83</v>
       </c>
       <c r="M34">
-        <v>16.44</v>
+        <v>3.42</v>
       </c>
       <c r="N34">
-        <v>15.74</v>
+        <v>3.45</v>
       </c>
       <c r="O34">
-        <v>14.19</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="35" spans="1:15">
@@ -3702,37 +3702,37 @@
         <v>552</v>
       </c>
       <c r="C35">
-        <v>10.34</v>
+        <v>14.02</v>
       </c>
       <c r="D35">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>-76.45999999999999</v>
+        <v>-60.75</v>
       </c>
       <c r="F35">
-        <v>41.2</v>
+        <v>35.36</v>
       </c>
       <c r="G35">
         <v>0.02</v>
       </c>
       <c r="J35">
-        <v>11.35</v>
+        <v>16.35</v>
       </c>
       <c r="K35">
-        <v>11.36</v>
+        <v>16.43</v>
       </c>
       <c r="L35">
-        <v>10.97</v>
+        <v>15.58</v>
       </c>
       <c r="M35">
-        <v>11.27</v>
+        <v>16.44</v>
       </c>
       <c r="N35">
-        <v>11.13</v>
+        <v>15.74</v>
       </c>
       <c r="O35">
-        <v>10.21</v>
+        <v>14.19</v>
       </c>
     </row>
     <row r="36" spans="1:15">
@@ -3743,43 +3743,37 @@
         <v>552</v>
       </c>
       <c r="C36">
-        <v>124.1</v>
+        <v>10.34</v>
       </c>
       <c r="D36">
-        <v>5.08</v>
+        <v>0.1</v>
       </c>
       <c r="E36">
-        <v>107.7</v>
+        <v>-76.45999999999999</v>
       </c>
       <c r="F36">
-        <v>61.91</v>
+        <v>41.2</v>
       </c>
       <c r="G36">
-        <v>0.84</v>
-      </c>
-      <c r="H36" t="s">
-        <v>561</v>
-      </c>
-      <c r="I36" t="s">
-        <v>617</v>
+        <v>0.02</v>
       </c>
       <c r="J36">
-        <v>107.88</v>
+        <v>11.35</v>
       </c>
       <c r="K36">
-        <v>110.6</v>
+        <v>11.36</v>
       </c>
       <c r="L36">
-        <v>118.4</v>
+        <v>10.97</v>
       </c>
       <c r="M36">
-        <v>108.84</v>
+        <v>11.27</v>
       </c>
       <c r="N36">
-        <v>110.79</v>
+        <v>11.13</v>
       </c>
       <c r="O36">
-        <v>116.38</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="37" spans="1:15">
@@ -3790,37 +3784,43 @@
         <v>552</v>
       </c>
       <c r="C37">
-        <v>28.94</v>
+        <v>124.1</v>
       </c>
       <c r="D37">
         <v>5.08</v>
       </c>
       <c r="E37">
-        <v>11.36</v>
+        <v>107.7</v>
       </c>
       <c r="F37">
-        <v>63.89</v>
+        <v>61.91</v>
       </c>
       <c r="G37">
-        <v>0.19</v>
+        <v>0.84</v>
+      </c>
+      <c r="H37" t="s">
+        <v>561</v>
+      </c>
+      <c r="I37" t="s">
+        <v>617</v>
       </c>
       <c r="J37">
-        <v>25.54</v>
+        <v>107.88</v>
       </c>
       <c r="K37">
-        <v>26.44</v>
+        <v>110.6</v>
       </c>
       <c r="L37">
-        <v>26.98</v>
+        <v>118.4</v>
       </c>
       <c r="M37">
-        <v>25.93</v>
+        <v>108.84</v>
       </c>
       <c r="N37">
-        <v>26.61</v>
+        <v>110.79</v>
       </c>
       <c r="O37">
-        <v>27</v>
+        <v>116.38</v>
       </c>
     </row>
     <row r="38" spans="1:15">
@@ -3831,37 +3831,37 @@
         <v>552</v>
       </c>
       <c r="C38">
-        <v>102.5</v>
+        <v>28.94</v>
       </c>
       <c r="D38">
-        <v>0.39</v>
+        <v>5.08</v>
       </c>
       <c r="E38">
-        <v>-82.73999999999999</v>
+        <v>11.36</v>
       </c>
       <c r="F38">
-        <v>78.18000000000001</v>
+        <v>63.89</v>
       </c>
       <c r="G38">
-        <v>1.83</v>
+        <v>0.19</v>
       </c>
       <c r="J38">
-        <v>77.87</v>
+        <v>25.54</v>
       </c>
       <c r="K38">
-        <v>80.81</v>
+        <v>26.44</v>
       </c>
       <c r="L38">
-        <v>89.7</v>
+        <v>26.98</v>
       </c>
       <c r="M38">
-        <v>78.97</v>
+        <v>25.93</v>
       </c>
       <c r="N38">
-        <v>88.89</v>
+        <v>26.61</v>
       </c>
       <c r="O38">
-        <v>94.69</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:15">
@@ -3872,43 +3872,37 @@
         <v>552</v>
       </c>
       <c r="C39">
-        <v>117</v>
+        <v>102.5</v>
       </c>
       <c r="D39">
-        <v>3.54</v>
+        <v>0.39</v>
       </c>
       <c r="E39">
-        <v>-15.98</v>
+        <v>-82.73999999999999</v>
       </c>
       <c r="F39">
-        <v>52.87</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="G39">
-        <v>0.3</v>
-      </c>
-      <c r="H39" t="s">
-        <v>562</v>
-      </c>
-      <c r="I39" t="s">
-        <v>620</v>
+        <v>1.83</v>
       </c>
       <c r="J39">
-        <v>113.26</v>
+        <v>77.87</v>
       </c>
       <c r="K39">
-        <v>116</v>
+        <v>80.81</v>
       </c>
       <c r="L39">
-        <v>117.66</v>
+        <v>89.7</v>
       </c>
       <c r="M39">
-        <v>115.67</v>
+        <v>78.97</v>
       </c>
       <c r="N39">
-        <v>116.3</v>
+        <v>88.89</v>
       </c>
       <c r="O39">
-        <v>112.62</v>
+        <v>94.69</v>
       </c>
     </row>
     <row r="40" spans="1:15">
@@ -3919,43 +3913,43 @@
         <v>552</v>
       </c>
       <c r="C40">
-        <v>42.26</v>
+        <v>117</v>
       </c>
       <c r="D40">
-        <v>1.73</v>
+        <v>3.54</v>
       </c>
       <c r="E40">
-        <v>-59.17</v>
+        <v>-15.98</v>
       </c>
       <c r="F40">
-        <v>53.36</v>
+        <v>52.87</v>
       </c>
       <c r="G40">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="H40" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I40" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="J40">
-        <v>36.67</v>
+        <v>113.26</v>
       </c>
       <c r="K40">
-        <v>40.49</v>
+        <v>116</v>
       </c>
       <c r="L40">
-        <v>42.31</v>
+        <v>117.66</v>
       </c>
       <c r="M40">
-        <v>37.13</v>
+        <v>115.67</v>
       </c>
       <c r="N40">
-        <v>41.6</v>
+        <v>116.3</v>
       </c>
       <c r="O40">
-        <v>40.51</v>
+        <v>112.62</v>
       </c>
     </row>
     <row r="41" spans="1:15">
@@ -3966,37 +3960,43 @@
         <v>552</v>
       </c>
       <c r="C41">
-        <v>24.86</v>
+        <v>42.26</v>
       </c>
       <c r="D41">
-        <v>-0.8</v>
+        <v>1.73</v>
       </c>
       <c r="E41">
-        <v>-36.88</v>
+        <v>-59.17</v>
       </c>
       <c r="F41">
-        <v>40.45</v>
+        <v>53.36</v>
       </c>
       <c r="G41">
-        <v>0.11</v>
+        <v>0.22</v>
+      </c>
+      <c r="H41" t="s">
+        <v>563</v>
+      </c>
+      <c r="I41" t="s">
+        <v>618</v>
       </c>
       <c r="J41">
-        <v>28.24</v>
+        <v>36.67</v>
       </c>
       <c r="K41">
-        <v>28.33</v>
+        <v>40.49</v>
       </c>
       <c r="L41">
-        <v>28.37</v>
+        <v>42.31</v>
       </c>
       <c r="M41">
-        <v>28.15</v>
+        <v>37.13</v>
       </c>
       <c r="N41">
-        <v>28.41</v>
+        <v>41.6</v>
       </c>
       <c r="O41">
-        <v>25.76</v>
+        <v>40.51</v>
       </c>
     </row>
     <row r="42" spans="1:15">
@@ -4007,37 +4007,37 @@
         <v>552</v>
       </c>
       <c r="C42">
-        <v>81</v>
+        <v>24.86</v>
       </c>
       <c r="D42">
-        <v>1.82</v>
+        <v>-0.8</v>
       </c>
       <c r="E42">
-        <v>-86.16</v>
+        <v>-36.88</v>
       </c>
       <c r="F42">
-        <v>53.34</v>
+        <v>40.45</v>
       </c>
       <c r="G42">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J42">
-        <v>56.67</v>
+        <v>28.24</v>
       </c>
       <c r="K42">
-        <v>60.07</v>
+        <v>28.33</v>
       </c>
       <c r="L42">
-        <v>81.98999999999999</v>
+        <v>28.37</v>
       </c>
       <c r="M42">
-        <v>57.55</v>
+        <v>28.15</v>
       </c>
       <c r="N42">
-        <v>64.37</v>
+        <v>28.41</v>
       </c>
       <c r="O42">
-        <v>79.36</v>
+        <v>25.76</v>
       </c>
     </row>
     <row r="43" spans="1:15">
@@ -4048,43 +4048,37 @@
         <v>552</v>
       </c>
       <c r="C43">
-        <v>4.23</v>
+        <v>81</v>
       </c>
       <c r="D43">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="E43">
-        <v>-52.05</v>
+        <v>-86.16</v>
       </c>
       <c r="F43">
-        <v>57.66</v>
+        <v>53.34</v>
       </c>
       <c r="G43">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H43" t="s">
-        <v>557</v>
-      </c>
-      <c r="I43" t="s">
-        <v>618</v>
+        <v>0.08</v>
       </c>
       <c r="J43">
-        <v>3.85</v>
+        <v>56.67</v>
       </c>
       <c r="K43">
-        <v>4.06</v>
+        <v>60.07</v>
       </c>
       <c r="L43">
-        <v>4.21</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="M43">
-        <v>3.9</v>
+        <v>57.55</v>
       </c>
       <c r="N43">
-        <v>4.12</v>
+        <v>64.37</v>
       </c>
       <c r="O43">
-        <v>3.94</v>
+        <v>79.36</v>
       </c>
     </row>
     <row r="44" spans="1:15">
@@ -4095,43 +4089,43 @@
         <v>552</v>
       </c>
       <c r="C44">
-        <v>39.34</v>
+        <v>4.23</v>
       </c>
       <c r="D44">
-        <v>2.18</v>
+        <v>1.68</v>
       </c>
       <c r="E44">
-        <v>-56.64</v>
+        <v>-52.05</v>
       </c>
       <c r="F44">
-        <v>54.8</v>
+        <v>57.66</v>
       </c>
       <c r="G44">
-        <v>0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H44" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="I44" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="J44">
-        <v>38.91</v>
+        <v>3.85</v>
       </c>
       <c r="K44">
-        <v>38.94</v>
+        <v>4.06</v>
       </c>
       <c r="L44">
-        <v>38.64</v>
+        <v>4.21</v>
       </c>
       <c r="M44">
-        <v>38.77</v>
+        <v>3.9</v>
       </c>
       <c r="N44">
-        <v>39.03</v>
+        <v>4.12</v>
       </c>
       <c r="O44">
-        <v>37.3</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="45" spans="1:15">
@@ -4142,43 +4136,43 @@
         <v>552</v>
       </c>
       <c r="C45">
-        <v>2.61</v>
+        <v>39.34</v>
       </c>
       <c r="D45">
-        <v>-0.38</v>
+        <v>2.18</v>
       </c>
       <c r="E45">
-        <v>-53.19</v>
+        <v>-56.64</v>
       </c>
       <c r="F45">
-        <v>46.98</v>
+        <v>54.8</v>
       </c>
       <c r="G45">
-        <v>-0.01</v>
+        <v>0.19</v>
       </c>
       <c r="H45" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="I45" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="J45">
-        <v>2.77</v>
+        <v>38.91</v>
       </c>
       <c r="K45">
-        <v>2.88</v>
+        <v>38.94</v>
       </c>
       <c r="L45">
-        <v>2.69</v>
+        <v>38.64</v>
       </c>
       <c r="M45">
-        <v>2.77</v>
+        <v>38.77</v>
       </c>
       <c r="N45">
-        <v>2.8</v>
+        <v>39.03</v>
       </c>
       <c r="O45">
-        <v>2.61</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="46" spans="1:15">
@@ -4189,19 +4183,19 @@
         <v>552</v>
       </c>
       <c r="C46">
-        <v>338.75</v>
+        <v>2.61</v>
       </c>
       <c r="D46">
-        <v>-2.87</v>
+        <v>-0.38</v>
       </c>
       <c r="E46">
-        <v>-70</v>
+        <v>-53.19</v>
       </c>
       <c r="F46">
-        <v>57.27</v>
+        <v>46.98</v>
       </c>
       <c r="G46">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="H46" t="s">
         <v>553</v>
@@ -4210,22 +4204,22 @@
         <v>616</v>
       </c>
       <c r="J46">
-        <v>261.47</v>
+        <v>2.77</v>
       </c>
       <c r="K46">
-        <v>312.17</v>
+        <v>2.88</v>
       </c>
       <c r="L46">
-        <v>334.98</v>
+        <v>2.69</v>
       </c>
       <c r="M46">
-        <v>277.79</v>
+        <v>2.77</v>
       </c>
       <c r="N46">
-        <v>316.48</v>
+        <v>2.8</v>
       </c>
       <c r="O46">
-        <v>340.38</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="47" spans="1:15">
@@ -4236,43 +4230,43 @@
         <v>552</v>
       </c>
       <c r="C47">
-        <v>187.3</v>
+        <v>338.75</v>
       </c>
       <c r="D47">
-        <v>1.13</v>
+        <v>-2.87</v>
       </c>
       <c r="E47">
-        <v>-60.42</v>
+        <v>-70</v>
       </c>
       <c r="F47">
-        <v>55.37</v>
+        <v>57.27</v>
       </c>
       <c r="G47">
-        <v>-1.2</v>
+        <v>0.06</v>
       </c>
       <c r="H47" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="I47" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="J47">
-        <v>162.17</v>
+        <v>261.47</v>
       </c>
       <c r="K47">
-        <v>185.37</v>
+        <v>312.17</v>
       </c>
       <c r="L47">
-        <v>191.32</v>
+        <v>334.98</v>
       </c>
       <c r="M47">
-        <v>146.19</v>
+        <v>277.79</v>
       </c>
       <c r="N47">
-        <v>182</v>
+        <v>316.48</v>
       </c>
       <c r="O47">
-        <v>185.67</v>
+        <v>340.38</v>
       </c>
     </row>
     <row r="48" spans="1:15">
@@ -4283,37 +4277,43 @@
         <v>552</v>
       </c>
       <c r="C48">
-        <v>66.3</v>
+        <v>187.3</v>
       </c>
       <c r="D48">
-        <v>-0.15</v>
+        <v>1.13</v>
       </c>
       <c r="E48">
-        <v>-86.48</v>
+        <v>-60.42</v>
       </c>
       <c r="F48">
-        <v>51.21</v>
+        <v>55.37</v>
       </c>
       <c r="G48">
-        <v>-0.21</v>
+        <v>-1.2</v>
+      </c>
+      <c r="H48" t="s">
+        <v>565</v>
+      </c>
+      <c r="I48" t="s">
+        <v>618</v>
       </c>
       <c r="J48">
-        <v>62.06</v>
+        <v>162.17</v>
       </c>
       <c r="K48">
-        <v>65.47</v>
+        <v>185.37</v>
       </c>
       <c r="L48">
-        <v>66.73999999999999</v>
+        <v>191.32</v>
       </c>
       <c r="M48">
-        <v>61.77</v>
+        <v>146.19</v>
       </c>
       <c r="N48">
-        <v>62.89</v>
+        <v>182</v>
       </c>
       <c r="O48">
-        <v>65.59</v>
+        <v>185.67</v>
       </c>
     </row>
     <row r="49" spans="1:15">
@@ -4324,37 +4324,37 @@
         <v>552</v>
       </c>
       <c r="C49">
-        <v>51.9</v>
+        <v>66.3</v>
       </c>
       <c r="D49">
-        <v>-0.57</v>
+        <v>-0.15</v>
       </c>
       <c r="E49">
-        <v>-59.67</v>
+        <v>-86.48</v>
       </c>
       <c r="F49">
-        <v>35.91</v>
+        <v>51.21</v>
       </c>
       <c r="G49">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="J49">
-        <v>57.67</v>
+        <v>62.06</v>
       </c>
       <c r="K49">
-        <v>57.8</v>
+        <v>65.47</v>
       </c>
       <c r="L49">
-        <v>56.14</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="M49">
-        <v>56.75</v>
+        <v>61.77</v>
       </c>
       <c r="N49">
-        <v>57.92</v>
+        <v>62.89</v>
       </c>
       <c r="O49">
-        <v>57.05</v>
+        <v>65.59</v>
       </c>
     </row>
     <row r="50" spans="1:15">
@@ -4365,37 +4365,37 @@
         <v>552</v>
       </c>
       <c r="C50">
-        <v>146.8</v>
+        <v>51.9</v>
       </c>
       <c r="D50">
-        <v>1.03</v>
+        <v>-0.57</v>
       </c>
       <c r="E50">
-        <v>-74.04000000000001</v>
+        <v>-59.67</v>
       </c>
       <c r="F50">
-        <v>44.84</v>
+        <v>35.91</v>
       </c>
       <c r="G50">
-        <v>-0.99</v>
+        <v>-0.23</v>
       </c>
       <c r="J50">
-        <v>155.03</v>
+        <v>57.67</v>
       </c>
       <c r="K50">
-        <v>159.88</v>
+        <v>57.8</v>
       </c>
       <c r="L50">
-        <v>157.22</v>
+        <v>56.14</v>
       </c>
       <c r="M50">
-        <v>153.6</v>
+        <v>56.75</v>
       </c>
       <c r="N50">
-        <v>157.44</v>
+        <v>57.92</v>
       </c>
       <c r="O50">
-        <v>159.81</v>
+        <v>57.05</v>
       </c>
     </row>
     <row r="51" spans="1:15">
@@ -4406,37 +4406,37 @@
         <v>552</v>
       </c>
       <c r="C51">
-        <v>109.5</v>
+        <v>146.8</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="E51">
-        <v>-72.51000000000001</v>
+        <v>-74.04000000000001</v>
       </c>
       <c r="F51">
-        <v>54.45</v>
+        <v>44.84</v>
       </c>
       <c r="G51">
-        <v>2.2</v>
+        <v>-0.99</v>
       </c>
       <c r="J51">
-        <v>114.35</v>
+        <v>155.03</v>
       </c>
       <c r="K51">
-        <v>113.03</v>
+        <v>159.88</v>
       </c>
       <c r="L51">
-        <v>106.24</v>
+        <v>157.22</v>
       </c>
       <c r="M51">
-        <v>113.59</v>
+        <v>153.6</v>
       </c>
       <c r="N51">
-        <v>115.6</v>
+        <v>157.44</v>
       </c>
       <c r="O51">
-        <v>103.46</v>
+        <v>159.81</v>
       </c>
     </row>
     <row r="52" spans="1:15">
@@ -4447,43 +4447,37 @@
         <v>552</v>
       </c>
       <c r="C52">
-        <v>8.94</v>
+        <v>109.5</v>
       </c>
       <c r="D52">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="E52">
-        <v>-76.84999999999999</v>
+        <v>-72.51000000000001</v>
       </c>
       <c r="F52">
-        <v>53.02</v>
+        <v>54.45</v>
       </c>
       <c r="G52">
-        <v>0.06</v>
-      </c>
-      <c r="H52" t="s">
-        <v>565</v>
-      </c>
-      <c r="I52" t="s">
-        <v>618</v>
+        <v>2.2</v>
       </c>
       <c r="J52">
-        <v>8.23</v>
+        <v>114.35</v>
       </c>
       <c r="K52">
-        <v>8.710000000000001</v>
+        <v>113.03</v>
       </c>
       <c r="L52">
-        <v>9.539999999999999</v>
+        <v>106.24</v>
       </c>
       <c r="M52">
-        <v>8.48</v>
+        <v>113.59</v>
       </c>
       <c r="N52">
-        <v>8.99</v>
+        <v>115.6</v>
       </c>
       <c r="O52">
-        <v>8.84</v>
+        <v>103.46</v>
       </c>
     </row>
     <row r="53" spans="1:15">
@@ -4494,37 +4488,43 @@
         <v>552</v>
       </c>
       <c r="C53">
-        <v>50.1</v>
+        <v>8.94</v>
       </c>
       <c r="D53">
-        <v>-1.76</v>
+        <v>3.71</v>
       </c>
       <c r="E53">
-        <v>4.45</v>
+        <v>-76.84999999999999</v>
       </c>
       <c r="F53">
-        <v>36.07</v>
+        <v>53.02</v>
       </c>
       <c r="G53">
-        <v>-0.03</v>
+        <v>0.06</v>
+      </c>
+      <c r="H53" t="s">
+        <v>565</v>
+      </c>
+      <c r="I53" t="s">
+        <v>618</v>
       </c>
       <c r="J53">
-        <v>68.98999999999999</v>
+        <v>8.23</v>
       </c>
       <c r="K53">
-        <v>61.51</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L53">
-        <v>54.7</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="M53">
-        <v>69.13</v>
+        <v>8.48</v>
       </c>
       <c r="N53">
-        <v>63.75</v>
+        <v>8.99</v>
       </c>
       <c r="O53">
-        <v>57.36</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="54" spans="1:15">
@@ -4535,37 +4535,37 @@
         <v>552</v>
       </c>
       <c r="C54">
-        <v>11.41</v>
+        <v>50.1</v>
       </c>
       <c r="D54">
-        <v>-0.78</v>
+        <v>-1.76</v>
       </c>
       <c r="E54">
-        <v>-85.7</v>
+        <v>4.45</v>
       </c>
       <c r="F54">
-        <v>37</v>
+        <v>36.07</v>
       </c>
       <c r="G54">
-        <v>-0.24</v>
+        <v>-0.03</v>
       </c>
       <c r="J54">
-        <v>12.11</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K54">
-        <v>11.76</v>
+        <v>61.51</v>
       </c>
       <c r="L54">
-        <v>13.51</v>
+        <v>54.7</v>
       </c>
       <c r="M54">
-        <v>12.47</v>
+        <v>69.13</v>
       </c>
       <c r="N54">
-        <v>11.7</v>
+        <v>63.75</v>
       </c>
       <c r="O54">
-        <v>12.05</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="55" spans="1:15">
@@ -4576,37 +4576,37 @@
         <v>552</v>
       </c>
       <c r="C55">
-        <v>36.58</v>
+        <v>11.41</v>
       </c>
       <c r="D55">
-        <v>0.66</v>
+        <v>-0.78</v>
       </c>
       <c r="E55">
-        <v>-77.45</v>
+        <v>-85.7</v>
       </c>
       <c r="F55">
-        <v>47.21</v>
+        <v>37</v>
       </c>
       <c r="G55">
-        <v>0.12</v>
+        <v>-0.24</v>
       </c>
       <c r="J55">
-        <v>38.67</v>
+        <v>12.11</v>
       </c>
       <c r="K55">
-        <v>38.93</v>
+        <v>11.76</v>
       </c>
       <c r="L55">
-        <v>37.09</v>
+        <v>13.51</v>
       </c>
       <c r="M55">
-        <v>38.73</v>
+        <v>12.47</v>
       </c>
       <c r="N55">
-        <v>38.24</v>
+        <v>11.7</v>
       </c>
       <c r="O55">
-        <v>36.21</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="56" spans="1:15">
@@ -4617,43 +4617,37 @@
         <v>552</v>
       </c>
       <c r="C56">
-        <v>4.72</v>
+        <v>36.58</v>
       </c>
       <c r="D56">
-        <v>-0.42</v>
+        <v>0.66</v>
       </c>
       <c r="E56">
-        <v>-69.28</v>
+        <v>-77.45</v>
       </c>
       <c r="F56">
-        <v>53.17</v>
+        <v>47.21</v>
       </c>
       <c r="G56">
-        <v>0.02</v>
-      </c>
-      <c r="H56" t="s">
-        <v>566</v>
-      </c>
-      <c r="I56" t="s">
-        <v>617</v>
+        <v>0.12</v>
       </c>
       <c r="J56">
-        <v>4.66</v>
+        <v>38.67</v>
       </c>
       <c r="K56">
-        <v>4.92</v>
+        <v>38.93</v>
       </c>
       <c r="L56">
-        <v>4.65</v>
+        <v>37.09</v>
       </c>
       <c r="M56">
-        <v>4.69</v>
+        <v>38.73</v>
       </c>
       <c r="N56">
-        <v>4.63</v>
+        <v>38.24</v>
       </c>
       <c r="O56">
-        <v>4.65</v>
+        <v>36.21</v>
       </c>
     </row>
     <row r="57" spans="1:15">
@@ -4664,37 +4658,43 @@
         <v>552</v>
       </c>
       <c r="C57">
-        <v>699.5</v>
+        <v>4.72</v>
       </c>
       <c r="D57">
-        <v>2.72</v>
+        <v>-0.42</v>
       </c>
       <c r="E57">
-        <v>-39.83</v>
+        <v>-69.28</v>
       </c>
       <c r="F57">
-        <v>68.42</v>
+        <v>53.17</v>
       </c>
       <c r="G57">
-        <v>11.52</v>
+        <v>0.02</v>
+      </c>
+      <c r="H57" t="s">
+        <v>566</v>
+      </c>
+      <c r="I57" t="s">
+        <v>617</v>
       </c>
       <c r="J57">
-        <v>518.21</v>
+        <v>4.66</v>
       </c>
       <c r="K57">
-        <v>530.73</v>
+        <v>4.92</v>
       </c>
       <c r="L57">
-        <v>616.24</v>
+        <v>4.65</v>
       </c>
       <c r="M57">
-        <v>526.15</v>
+        <v>4.69</v>
       </c>
       <c r="N57">
-        <v>555.38</v>
+        <v>4.63</v>
       </c>
       <c r="O57">
-        <v>651.86</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="58" spans="1:15">
@@ -4705,37 +4705,37 @@
         <v>552</v>
       </c>
       <c r="C58">
-        <v>26.82</v>
+        <v>699.5</v>
       </c>
       <c r="D58">
-        <v>1.9</v>
+        <v>2.72</v>
       </c>
       <c r="E58">
-        <v>-50.44</v>
+        <v>-39.83</v>
       </c>
       <c r="F58">
-        <v>56.52</v>
+        <v>68.42</v>
       </c>
       <c r="G58">
-        <v>-0.07000000000000001</v>
+        <v>11.52</v>
       </c>
       <c r="J58">
-        <v>24.66</v>
+        <v>518.21</v>
       </c>
       <c r="K58">
-        <v>25.96</v>
+        <v>530.73</v>
       </c>
       <c r="L58">
-        <v>26.09</v>
+        <v>616.24</v>
       </c>
       <c r="M58">
-        <v>24.35</v>
+        <v>526.15</v>
       </c>
       <c r="N58">
-        <v>24.87</v>
+        <v>555.38</v>
       </c>
       <c r="O58">
-        <v>26.04</v>
+        <v>651.86</v>
       </c>
     </row>
     <row r="59" spans="1:15">
@@ -4746,37 +4746,37 @@
         <v>552</v>
       </c>
       <c r="C59">
-        <v>27.84</v>
+        <v>26.82</v>
       </c>
       <c r="D59">
-        <v>0.58</v>
+        <v>1.9</v>
       </c>
       <c r="E59">
-        <v>-43.92</v>
+        <v>-50.44</v>
       </c>
       <c r="F59">
-        <v>48.24</v>
+        <v>56.52</v>
       </c>
       <c r="G59">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J59">
-        <v>28.8</v>
+        <v>24.66</v>
       </c>
       <c r="K59">
-        <v>28.81</v>
+        <v>25.96</v>
       </c>
       <c r="L59">
-        <v>28.06</v>
+        <v>26.09</v>
       </c>
       <c r="M59">
-        <v>28.29</v>
+        <v>24.35</v>
       </c>
       <c r="N59">
-        <v>28.97</v>
+        <v>24.87</v>
       </c>
       <c r="O59">
-        <v>28.12</v>
+        <v>26.04</v>
       </c>
     </row>
     <row r="60" spans="1:15">
@@ -4787,37 +4787,37 @@
         <v>552</v>
       </c>
       <c r="C60">
-        <v>32</v>
+        <v>27.84</v>
       </c>
       <c r="D60">
-        <v>-1.54</v>
+        <v>0.58</v>
       </c>
       <c r="E60">
-        <v>-45.73</v>
+        <v>-43.92</v>
       </c>
       <c r="F60">
-        <v>72.98</v>
+        <v>48.24</v>
       </c>
       <c r="G60">
-        <v>0.45</v>
+        <v>-0.08</v>
       </c>
       <c r="J60">
-        <v>22.92</v>
+        <v>28.8</v>
       </c>
       <c r="K60">
-        <v>24.37</v>
+        <v>28.81</v>
       </c>
       <c r="L60">
-        <v>27.91</v>
+        <v>28.06</v>
       </c>
       <c r="M60">
-        <v>23.59</v>
+        <v>28.29</v>
       </c>
       <c r="N60">
-        <v>24.61</v>
+        <v>28.97</v>
       </c>
       <c r="O60">
-        <v>28.15</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="61" spans="1:15">
@@ -4828,43 +4828,37 @@
         <v>552</v>
       </c>
       <c r="C61">
-        <v>250.25</v>
+        <v>32</v>
       </c>
       <c r="D61">
-        <v>4.18</v>
+        <v>-1.54</v>
       </c>
       <c r="E61">
-        <v>-2.18</v>
+        <v>-45.73</v>
       </c>
       <c r="F61">
-        <v>53.39</v>
+        <v>72.98</v>
       </c>
       <c r="G61">
-        <v>-1.81</v>
-      </c>
-      <c r="H61" t="s">
-        <v>557</v>
-      </c>
-      <c r="I61" t="s">
-        <v>618</v>
+        <v>0.45</v>
       </c>
       <c r="J61">
-        <v>234.11</v>
+        <v>22.92</v>
       </c>
       <c r="K61">
-        <v>236.18</v>
+        <v>24.37</v>
       </c>
       <c r="L61">
-        <v>249.91</v>
+        <v>27.91</v>
       </c>
       <c r="M61">
-        <v>230.32</v>
+        <v>23.59</v>
       </c>
       <c r="N61">
-        <v>234.99</v>
+        <v>24.61</v>
       </c>
       <c r="O61">
-        <v>239.39</v>
+        <v>28.15</v>
       </c>
     </row>
     <row r="62" spans="1:15">
@@ -4875,37 +4869,43 @@
         <v>552</v>
       </c>
       <c r="C62">
-        <v>4.08</v>
+        <v>250.25</v>
       </c>
       <c r="D62">
-        <v>0.25</v>
+        <v>4.18</v>
       </c>
       <c r="E62">
-        <v>-70.56999999999999</v>
+        <v>-2.18</v>
       </c>
       <c r="F62">
-        <v>40.18</v>
+        <v>53.39</v>
       </c>
       <c r="G62">
-        <v>-0.02</v>
+        <v>-1.81</v>
+      </c>
+      <c r="H62" t="s">
+        <v>557</v>
+      </c>
+      <c r="I62" t="s">
+        <v>618</v>
       </c>
       <c r="J62">
-        <v>4.49</v>
+        <v>234.11</v>
       </c>
       <c r="K62">
-        <v>4.54</v>
+        <v>236.18</v>
       </c>
       <c r="L62">
-        <v>4.22</v>
+        <v>249.91</v>
       </c>
       <c r="M62">
-        <v>4.49</v>
+        <v>230.32</v>
       </c>
       <c r="N62">
-        <v>4.51</v>
+        <v>234.99</v>
       </c>
       <c r="O62">
-        <v>4.25</v>
+        <v>239.39</v>
       </c>
     </row>
     <row r="63" spans="1:15">
@@ -4916,37 +4916,37 @@
         <v>552</v>
       </c>
       <c r="C63">
-        <v>39.32</v>
+        <v>4.08</v>
       </c>
       <c r="D63">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="E63">
-        <v>-60.25</v>
+        <v>-70.56999999999999</v>
       </c>
       <c r="F63">
-        <v>66.81999999999999</v>
+        <v>40.18</v>
       </c>
       <c r="G63">
-        <v>0.32</v>
+        <v>-0.02</v>
       </c>
       <c r="J63">
-        <v>32.72</v>
+        <v>4.49</v>
       </c>
       <c r="K63">
-        <v>34.55</v>
+        <v>4.54</v>
       </c>
       <c r="L63">
-        <v>36.05</v>
+        <v>4.22</v>
       </c>
       <c r="M63">
-        <v>33.01</v>
+        <v>4.49</v>
       </c>
       <c r="N63">
-        <v>35.44</v>
+        <v>4.51</v>
       </c>
       <c r="O63">
-        <v>36.76</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="64" spans="1:15">
@@ -4957,37 +4957,37 @@
         <v>552</v>
       </c>
       <c r="C64">
-        <v>143</v>
+        <v>39.32</v>
       </c>
       <c r="D64">
-        <v>3.1</v>
+        <v>0.36</v>
       </c>
       <c r="E64">
-        <v>-56.42</v>
+        <v>-60.25</v>
       </c>
       <c r="F64">
-        <v>67.29000000000001</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="G64">
-        <v>2.16</v>
+        <v>0.32</v>
       </c>
       <c r="J64">
-        <v>90.23999999999999</v>
+        <v>32.72</v>
       </c>
       <c r="K64">
-        <v>118.27</v>
+        <v>34.55</v>
       </c>
       <c r="L64">
-        <v>122.05</v>
+        <v>36.05</v>
       </c>
       <c r="M64">
-        <v>91.81</v>
+        <v>33.01</v>
       </c>
       <c r="N64">
-        <v>121.22</v>
+        <v>35.44</v>
       </c>
       <c r="O64">
-        <v>120.93</v>
+        <v>36.76</v>
       </c>
     </row>
     <row r="65" spans="1:15">
@@ -4998,37 +4998,37 @@
         <v>552</v>
       </c>
       <c r="C65">
-        <v>37.84</v>
+        <v>143</v>
       </c>
       <c r="D65">
-        <v>0.21</v>
+        <v>3.1</v>
       </c>
       <c r="E65">
-        <v>-78.61</v>
+        <v>-56.42</v>
       </c>
       <c r="F65">
-        <v>44.71</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="G65">
-        <v>0.05</v>
+        <v>2.16</v>
       </c>
       <c r="J65">
-        <v>40.22</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="K65">
-        <v>40.75</v>
+        <v>118.27</v>
       </c>
       <c r="L65">
-        <v>39.7</v>
+        <v>122.05</v>
       </c>
       <c r="M65">
-        <v>40.44</v>
+        <v>91.81</v>
       </c>
       <c r="N65">
-        <v>40.14</v>
+        <v>121.22</v>
       </c>
       <c r="O65">
-        <v>37.18</v>
+        <v>120.93</v>
       </c>
     </row>
     <row r="66" spans="1:15">
@@ -5039,43 +5039,37 @@
         <v>552</v>
       </c>
       <c r="C66">
-        <v>103</v>
+        <v>37.84</v>
       </c>
       <c r="D66">
-        <v>-4.98</v>
+        <v>0.21</v>
       </c>
       <c r="E66">
-        <v>-65.45999999999999</v>
+        <v>-78.61</v>
       </c>
       <c r="F66">
-        <v>54.01</v>
+        <v>44.71</v>
       </c>
       <c r="G66">
-        <v>1.4</v>
-      </c>
-      <c r="H66" t="s">
-        <v>567</v>
-      </c>
-      <c r="I66" t="s">
-        <v>616</v>
+        <v>0.05</v>
       </c>
       <c r="J66">
-        <v>96.69</v>
+        <v>40.22</v>
       </c>
       <c r="K66">
-        <v>103.25</v>
+        <v>40.75</v>
       </c>
       <c r="L66">
-        <v>100.18</v>
+        <v>39.7</v>
       </c>
       <c r="M66">
-        <v>99.45</v>
+        <v>40.44</v>
       </c>
       <c r="N66">
-        <v>101.71</v>
+        <v>40.14</v>
       </c>
       <c r="O66">
-        <v>98.66</v>
+        <v>37.18</v>
       </c>
     </row>
     <row r="67" spans="1:15">
@@ -5086,37 +5080,43 @@
         <v>552</v>
       </c>
       <c r="C67">
-        <v>14.16</v>
+        <v>103</v>
       </c>
       <c r="D67">
-        <v>-0.14</v>
+        <v>-4.98</v>
       </c>
       <c r="E67">
-        <v>-77.77</v>
+        <v>-65.45999999999999</v>
       </c>
       <c r="F67">
-        <v>38.02</v>
+        <v>54.01</v>
       </c>
       <c r="G67">
-        <v>0.03</v>
+        <v>1.4</v>
+      </c>
+      <c r="H67" t="s">
+        <v>567</v>
+      </c>
+      <c r="I67" t="s">
+        <v>616</v>
       </c>
       <c r="J67">
-        <v>16.85</v>
+        <v>96.69</v>
       </c>
       <c r="K67">
-        <v>16.64</v>
+        <v>103.25</v>
       </c>
       <c r="L67">
-        <v>16.22</v>
+        <v>100.18</v>
       </c>
       <c r="M67">
-        <v>16.71</v>
+        <v>99.45</v>
       </c>
       <c r="N67">
-        <v>16.28</v>
+        <v>101.71</v>
       </c>
       <c r="O67">
-        <v>14.2</v>
+        <v>98.66</v>
       </c>
     </row>
     <row r="68" spans="1:15">
@@ -5127,37 +5127,37 @@
         <v>552</v>
       </c>
       <c r="C68">
-        <v>154.3</v>
+        <v>14.16</v>
       </c>
       <c r="D68">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="E68">
-        <v>-69.03</v>
+        <v>-77.77</v>
       </c>
       <c r="F68">
-        <v>35.73</v>
+        <v>38.02</v>
       </c>
       <c r="G68">
-        <v>-0.17</v>
+        <v>0.03</v>
       </c>
       <c r="J68">
-        <v>170.15</v>
+        <v>16.85</v>
       </c>
       <c r="K68">
-        <v>170.94</v>
+        <v>16.64</v>
       </c>
       <c r="L68">
-        <v>166.15</v>
+        <v>16.22</v>
       </c>
       <c r="M68">
-        <v>169.5</v>
+        <v>16.71</v>
       </c>
       <c r="N68">
-        <v>170.64</v>
+        <v>16.28</v>
       </c>
       <c r="O68">
-        <v>168.98</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="69" spans="1:15">
@@ -5168,37 +5168,37 @@
         <v>552</v>
       </c>
       <c r="C69">
-        <v>48</v>
+        <v>154.3</v>
       </c>
       <c r="D69">
-        <v>-3.07</v>
+        <v>-0.13</v>
       </c>
       <c r="E69">
-        <v>14.79</v>
+        <v>-69.03</v>
       </c>
       <c r="F69">
-        <v>59.54</v>
+        <v>35.73</v>
       </c>
       <c r="G69">
-        <v>0.38</v>
+        <v>-0.17</v>
       </c>
       <c r="J69">
-        <v>40.68</v>
+        <v>170.15</v>
       </c>
       <c r="K69">
-        <v>43.57</v>
+        <v>170.94</v>
       </c>
       <c r="L69">
-        <v>45.18</v>
+        <v>166.15</v>
       </c>
       <c r="M69">
-        <v>41.96</v>
+        <v>169.5</v>
       </c>
       <c r="N69">
-        <v>44.25</v>
+        <v>170.64</v>
       </c>
       <c r="O69">
-        <v>44.93</v>
+        <v>168.98</v>
       </c>
     </row>
     <row r="70" spans="1:15">
@@ -5209,43 +5209,37 @@
         <v>552</v>
       </c>
       <c r="C70">
-        <v>14.78</v>
+        <v>48</v>
       </c>
       <c r="D70">
-        <v>1.93</v>
+        <v>-3.07</v>
       </c>
       <c r="E70">
-        <v>10.08</v>
+        <v>14.79</v>
       </c>
       <c r="F70">
-        <v>52.18</v>
+        <v>59.54</v>
       </c>
       <c r="G70">
-        <v>0.03</v>
-      </c>
-      <c r="H70" t="s">
-        <v>562</v>
-      </c>
-      <c r="I70" t="s">
-        <v>620</v>
+        <v>0.38</v>
       </c>
       <c r="J70">
-        <v>14.71</v>
+        <v>40.68</v>
       </c>
       <c r="K70">
-        <v>14.7</v>
+        <v>43.57</v>
       </c>
       <c r="L70">
-        <v>15.31</v>
+        <v>45.18</v>
       </c>
       <c r="M70">
-        <v>14.69</v>
+        <v>41.96</v>
       </c>
       <c r="N70">
-        <v>14.71</v>
+        <v>44.25</v>
       </c>
       <c r="O70">
-        <v>14.37</v>
+        <v>44.93</v>
       </c>
     </row>
     <row r="71" spans="1:15">
@@ -5256,37 +5250,43 @@
         <v>552</v>
       </c>
       <c r="C71">
-        <v>52.05</v>
+        <v>14.78</v>
       </c>
       <c r="D71">
-        <v>3.07</v>
+        <v>1.93</v>
       </c>
       <c r="E71">
-        <v>-60.22</v>
+        <v>10.08</v>
       </c>
       <c r="F71">
-        <v>69.83</v>
+        <v>52.18</v>
       </c>
       <c r="G71">
-        <v>0.35</v>
+        <v>0.03</v>
+      </c>
+      <c r="H71" t="s">
+        <v>562</v>
+      </c>
+      <c r="I71" t="s">
+        <v>620</v>
       </c>
       <c r="J71">
-        <v>46.58</v>
+        <v>14.71</v>
       </c>
       <c r="K71">
-        <v>48.09</v>
+        <v>14.7</v>
       </c>
       <c r="L71">
-        <v>48.65</v>
+        <v>15.31</v>
       </c>
       <c r="M71">
-        <v>46.78</v>
+        <v>14.69</v>
       </c>
       <c r="N71">
-        <v>48.29</v>
+        <v>14.71</v>
       </c>
       <c r="O71">
-        <v>48.14</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="72" spans="1:15">
@@ -5297,43 +5297,37 @@
         <v>552</v>
       </c>
       <c r="C72">
-        <v>4.55</v>
+        <v>52.05</v>
       </c>
       <c r="D72">
-        <v>-0.87</v>
+        <v>3.07</v>
       </c>
       <c r="E72">
-        <v>-84.06999999999999</v>
+        <v>-60.22</v>
       </c>
       <c r="F72">
-        <v>47.13</v>
+        <v>69.83</v>
       </c>
       <c r="G72">
-        <v>0.02</v>
-      </c>
-      <c r="H72" t="s">
-        <v>553</v>
-      </c>
-      <c r="I72" t="s">
-        <v>616</v>
+        <v>0.35</v>
       </c>
       <c r="J72">
-        <v>5.41</v>
+        <v>46.58</v>
       </c>
       <c r="K72">
-        <v>5.15</v>
+        <v>48.09</v>
       </c>
       <c r="L72">
-        <v>4.65</v>
+        <v>48.65</v>
       </c>
       <c r="M72">
-        <v>5.22</v>
+        <v>46.78</v>
       </c>
       <c r="N72">
-        <v>4.71</v>
+        <v>48.29</v>
       </c>
       <c r="O72">
-        <v>4.59</v>
+        <v>48.14</v>
       </c>
     </row>
     <row r="73" spans="1:15">
@@ -5344,37 +5338,43 @@
         <v>552</v>
       </c>
       <c r="C73">
-        <v>4.21</v>
+        <v>4.55</v>
       </c>
       <c r="D73">
-        <v>-0.71</v>
+        <v>-0.87</v>
       </c>
       <c r="E73">
-        <v>-37.39</v>
+        <v>-84.06999999999999</v>
       </c>
       <c r="F73">
-        <v>39.77</v>
+        <v>47.13</v>
       </c>
       <c r="G73">
         <v>0.02</v>
       </c>
+      <c r="H73" t="s">
+        <v>553</v>
+      </c>
+      <c r="I73" t="s">
+        <v>616</v>
+      </c>
       <c r="J73">
-        <v>5.1</v>
+        <v>5.41</v>
       </c>
       <c r="K73">
-        <v>4.82</v>
+        <v>5.15</v>
       </c>
       <c r="L73">
-        <v>4.72</v>
+        <v>4.65</v>
       </c>
       <c r="M73">
-        <v>4.88</v>
+        <v>5.22</v>
       </c>
       <c r="N73">
-        <v>4.74</v>
+        <v>4.71</v>
       </c>
       <c r="O73">
-        <v>4.17</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="74" spans="1:15">
@@ -5385,37 +5385,37 @@
         <v>552</v>
       </c>
       <c r="C74">
-        <v>17.13</v>
+        <v>4.21</v>
       </c>
       <c r="D74">
-        <v>-0.98</v>
+        <v>-0.71</v>
       </c>
       <c r="E74">
-        <v>-57.83</v>
+        <v>-37.39</v>
       </c>
       <c r="F74">
-        <v>42.11</v>
+        <v>39.77</v>
       </c>
       <c r="G74">
-        <v>-0.17</v>
+        <v>0.02</v>
       </c>
       <c r="J74">
-        <v>18.89</v>
+        <v>5.1</v>
       </c>
       <c r="K74">
-        <v>19.15</v>
+        <v>4.82</v>
       </c>
       <c r="L74">
-        <v>18.9</v>
+        <v>4.72</v>
       </c>
       <c r="M74">
-        <v>18.75</v>
+        <v>4.88</v>
       </c>
       <c r="N74">
-        <v>19.07</v>
+        <v>4.74</v>
       </c>
       <c r="O74">
-        <v>18.69</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="75" spans="1:15">
@@ -5426,37 +5426,37 @@
         <v>552</v>
       </c>
       <c r="C75">
-        <v>13.7</v>
+        <v>17.13</v>
       </c>
       <c r="D75">
-        <v>-0.87</v>
+        <v>-0.98</v>
       </c>
       <c r="E75">
-        <v>-85.48999999999999</v>
+        <v>-57.83</v>
       </c>
       <c r="F75">
-        <v>42.19</v>
+        <v>42.11</v>
       </c>
       <c r="G75">
-        <v>-0.1</v>
+        <v>-0.17</v>
       </c>
       <c r="J75">
-        <v>14.21</v>
+        <v>18.89</v>
       </c>
       <c r="K75">
-        <v>14.76</v>
+        <v>19.15</v>
       </c>
       <c r="L75">
-        <v>14.6</v>
+        <v>18.9</v>
       </c>
       <c r="M75">
-        <v>14.1</v>
+        <v>18.75</v>
       </c>
       <c r="N75">
-        <v>14.39</v>
+        <v>19.07</v>
       </c>
       <c r="O75">
-        <v>14.78</v>
+        <v>18.69</v>
       </c>
     </row>
     <row r="76" spans="1:15">
@@ -5467,43 +5467,37 @@
         <v>552</v>
       </c>
       <c r="C76">
-        <v>28.46</v>
+        <v>13.7</v>
       </c>
       <c r="D76">
-        <v>-0.14</v>
+        <v>-0.87</v>
       </c>
       <c r="E76">
-        <v>-41.85</v>
+        <v>-85.48999999999999</v>
       </c>
       <c r="F76">
-        <v>46.89</v>
+        <v>42.19</v>
       </c>
       <c r="G76">
-        <v>0.04</v>
-      </c>
-      <c r="H76" t="s">
-        <v>568</v>
-      </c>
-      <c r="I76" t="s">
-        <v>619</v>
+        <v>-0.1</v>
       </c>
       <c r="J76">
-        <v>29.85</v>
+        <v>14.21</v>
       </c>
       <c r="K76">
-        <v>29.75</v>
+        <v>14.76</v>
       </c>
       <c r="L76">
-        <v>29.16</v>
+        <v>14.6</v>
       </c>
       <c r="M76">
-        <v>29.78</v>
+        <v>14.1</v>
       </c>
       <c r="N76">
-        <v>29.62</v>
+        <v>14.39</v>
       </c>
       <c r="O76">
-        <v>28.55</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="77" spans="1:15">
@@ -5514,37 +5508,43 @@
         <v>552</v>
       </c>
       <c r="C77">
-        <v>141.8</v>
+        <v>28.46</v>
       </c>
       <c r="D77">
-        <v>0.28</v>
+        <v>-0.14</v>
       </c>
       <c r="E77">
-        <v>-58.54</v>
+        <v>-41.85</v>
       </c>
       <c r="F77">
-        <v>35.5</v>
+        <v>46.89</v>
       </c>
       <c r="G77">
-        <v>-0.11</v>
+        <v>0.04</v>
+      </c>
+      <c r="H77" t="s">
+        <v>568</v>
+      </c>
+      <c r="I77" t="s">
+        <v>619</v>
       </c>
       <c r="J77">
-        <v>159.64</v>
+        <v>29.85</v>
       </c>
       <c r="K77">
-        <v>157.74</v>
+        <v>29.75</v>
       </c>
       <c r="L77">
-        <v>152.84</v>
+        <v>29.16</v>
       </c>
       <c r="M77">
-        <v>159.9</v>
+        <v>29.78</v>
       </c>
       <c r="N77">
-        <v>157.85</v>
+        <v>29.62</v>
       </c>
       <c r="O77">
-        <v>157.54</v>
+        <v>28.55</v>
       </c>
     </row>
     <row r="78" spans="1:15">
@@ -5555,43 +5555,37 @@
         <v>552</v>
       </c>
       <c r="C78">
-        <v>23.42</v>
+        <v>141.8</v>
       </c>
       <c r="D78">
-        <v>1.12</v>
+        <v>0.28</v>
       </c>
       <c r="E78">
-        <v>-34.93</v>
+        <v>-58.54</v>
       </c>
       <c r="F78">
-        <v>49.05</v>
+        <v>35.5</v>
       </c>
       <c r="G78">
-        <v>0.09</v>
-      </c>
-      <c r="H78" t="s">
-        <v>558</v>
-      </c>
-      <c r="I78" t="s">
-        <v>618</v>
+        <v>-0.11</v>
       </c>
       <c r="J78">
-        <v>27.4</v>
+        <v>159.64</v>
       </c>
       <c r="K78">
-        <v>24.98</v>
+        <v>157.74</v>
       </c>
       <c r="L78">
-        <v>23.94</v>
+        <v>152.84</v>
       </c>
       <c r="M78">
-        <v>25.22</v>
+        <v>159.9</v>
       </c>
       <c r="N78">
-        <v>24.22</v>
+        <v>157.85</v>
       </c>
       <c r="O78">
-        <v>23.33</v>
+        <v>157.54</v>
       </c>
     </row>
     <row r="79" spans="1:15">
@@ -5602,37 +5596,43 @@
         <v>552</v>
       </c>
       <c r="C79">
-        <v>6.79</v>
+        <v>23.42</v>
       </c>
       <c r="D79">
-        <v>-0.59</v>
+        <v>1.12</v>
       </c>
       <c r="E79">
-        <v>-67.34</v>
+        <v>-34.93</v>
       </c>
       <c r="F79">
-        <v>27.78</v>
+        <v>49.05</v>
       </c>
       <c r="G79">
-        <v>0.01</v>
+        <v>0.09</v>
+      </c>
+      <c r="H79" t="s">
+        <v>558</v>
+      </c>
+      <c r="I79" t="s">
+        <v>618</v>
       </c>
       <c r="J79">
-        <v>10.66</v>
+        <v>27.4</v>
       </c>
       <c r="K79">
-        <v>10</v>
+        <v>24.98</v>
       </c>
       <c r="L79">
-        <v>8.56</v>
+        <v>23.94</v>
       </c>
       <c r="M79">
-        <v>10.52</v>
+        <v>25.22</v>
       </c>
       <c r="N79">
-        <v>9.24</v>
+        <v>24.22</v>
       </c>
       <c r="O79">
-        <v>7.15</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="80" spans="1:15">
@@ -5643,37 +5643,37 @@
         <v>552</v>
       </c>
       <c r="C80">
-        <v>8.69</v>
+        <v>6.79</v>
       </c>
       <c r="D80">
-        <v>-0.23</v>
+        <v>-0.59</v>
       </c>
       <c r="E80">
-        <v>-74.48999999999999</v>
+        <v>-67.34</v>
       </c>
       <c r="F80">
-        <v>41.55</v>
+        <v>27.78</v>
       </c>
       <c r="G80">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J80">
-        <v>9.67</v>
+        <v>10.66</v>
       </c>
       <c r="K80">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="L80">
-        <v>9.529999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="M80">
-        <v>9.49</v>
+        <v>10.52</v>
       </c>
       <c r="N80">
-        <v>9.51</v>
+        <v>9.24</v>
       </c>
       <c r="O80">
-        <v>8.74</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="81" spans="1:15">
@@ -5684,37 +5684,37 @@
         <v>552</v>
       </c>
       <c r="C81">
-        <v>243.8</v>
+        <v>8.69</v>
       </c>
       <c r="D81">
-        <v>0.62</v>
+        <v>-0.23</v>
       </c>
       <c r="E81">
-        <v>-8.029999999999999</v>
+        <v>-74.48999999999999</v>
       </c>
       <c r="F81">
-        <v>35.04</v>
+        <v>41.55</v>
       </c>
       <c r="G81">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="J81">
-        <v>322.67</v>
+        <v>9.67</v>
       </c>
       <c r="K81">
-        <v>306.57</v>
+        <v>9.5</v>
       </c>
       <c r="L81">
-        <v>273.96</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="M81">
-        <v>330.4</v>
+        <v>9.49</v>
       </c>
       <c r="N81">
-        <v>317.76</v>
+        <v>9.51</v>
       </c>
       <c r="O81">
-        <v>282.24</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="82" spans="1:15">
@@ -5725,43 +5725,37 @@
         <v>552</v>
       </c>
       <c r="C82">
-        <v>692</v>
+        <v>243.8</v>
       </c>
       <c r="D82">
-        <v>2.52</v>
+        <v>0.62</v>
       </c>
       <c r="E82">
-        <v>-41.4</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="F82">
-        <v>55.25</v>
+        <v>35.04</v>
       </c>
       <c r="G82">
-        <v>1.12</v>
-      </c>
-      <c r="H82" t="s">
-        <v>569</v>
-      </c>
-      <c r="I82" t="s">
-        <v>618</v>
+        <v>-0.03</v>
       </c>
       <c r="J82">
-        <v>614.37</v>
+        <v>322.67</v>
       </c>
       <c r="K82">
-        <v>639.22</v>
+        <v>306.57</v>
       </c>
       <c r="L82">
-        <v>680.7</v>
+        <v>273.96</v>
       </c>
       <c r="M82">
-        <v>629.9</v>
+        <v>330.4</v>
       </c>
       <c r="N82">
-        <v>652.9299999999999</v>
+        <v>317.76</v>
       </c>
       <c r="O82">
-        <v>684.2</v>
+        <v>282.24</v>
       </c>
     </row>
     <row r="83" spans="1:15">
@@ -5772,37 +5766,43 @@
         <v>552</v>
       </c>
       <c r="C83">
-        <v>159.9</v>
+        <v>692</v>
       </c>
       <c r="D83">
-        <v>-0.12</v>
+        <v>2.52</v>
       </c>
       <c r="E83">
-        <v>-33.68</v>
+        <v>-41.4</v>
       </c>
       <c r="F83">
-        <v>40.86</v>
+        <v>55.25</v>
       </c>
       <c r="G83">
-        <v>0.52</v>
+        <v>1.12</v>
+      </c>
+      <c r="H83" t="s">
+        <v>569</v>
+      </c>
+      <c r="I83" t="s">
+        <v>618</v>
       </c>
       <c r="J83">
-        <v>182.42</v>
+        <v>614.37</v>
       </c>
       <c r="K83">
-        <v>181.31</v>
+        <v>639.22</v>
       </c>
       <c r="L83">
-        <v>177.08</v>
+        <v>680.7</v>
       </c>
       <c r="M83">
-        <v>181.6</v>
+        <v>629.9</v>
       </c>
       <c r="N83">
-        <v>181.23</v>
+        <v>652.9299999999999</v>
       </c>
       <c r="O83">
-        <v>162.82</v>
+        <v>684.2</v>
       </c>
     </row>
     <row r="84" spans="1:15">
@@ -5813,37 +5813,37 @@
         <v>552</v>
       </c>
       <c r="C84">
-        <v>8.41</v>
+        <v>159.9</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="E84">
-        <v>-57.49</v>
+        <v>-33.68</v>
       </c>
       <c r="F84">
-        <v>40.32</v>
+        <v>40.86</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="J84">
-        <v>10.03</v>
+        <v>182.42</v>
       </c>
       <c r="K84">
-        <v>9.68</v>
+        <v>181.31</v>
       </c>
       <c r="L84">
-        <v>9.699999999999999</v>
+        <v>177.08</v>
       </c>
       <c r="M84">
-        <v>9.699999999999999</v>
+        <v>181.6</v>
       </c>
       <c r="N84">
-        <v>9.720000000000001</v>
+        <v>181.23</v>
       </c>
       <c r="O84">
-        <v>8.44</v>
+        <v>162.82</v>
       </c>
     </row>
     <row r="85" spans="1:15">
@@ -5854,37 +5854,37 @@
         <v>552</v>
       </c>
       <c r="C85">
-        <v>27.2</v>
+        <v>8.41</v>
       </c>
       <c r="D85">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="E85">
-        <v>-67.27</v>
+        <v>-57.49</v>
       </c>
       <c r="F85">
-        <v>38.96</v>
+        <v>40.32</v>
       </c>
       <c r="G85">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="J85">
-        <v>29.22</v>
+        <v>10.03</v>
       </c>
       <c r="K85">
-        <v>29.96</v>
+        <v>9.68</v>
       </c>
       <c r="L85">
-        <v>30.12</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M85">
-        <v>29</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N85">
-        <v>29.37</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="O85">
-        <v>30.22</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="86" spans="1:15">
@@ -5895,37 +5895,37 @@
         <v>552</v>
       </c>
       <c r="C86">
-        <v>1.51</v>
+        <v>27.2</v>
       </c>
       <c r="D86">
-        <v>1.34</v>
+        <v>0.22</v>
       </c>
       <c r="E86">
-        <v>-55.75</v>
+        <v>-67.27</v>
       </c>
       <c r="F86">
-        <v>46.86</v>
+        <v>38.96</v>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="J86">
-        <v>1.63</v>
+        <v>29.22</v>
       </c>
       <c r="K86">
-        <v>1.6</v>
+        <v>29.96</v>
       </c>
       <c r="L86">
-        <v>1.58</v>
+        <v>30.12</v>
       </c>
       <c r="M86">
-        <v>1.62</v>
+        <v>29</v>
       </c>
       <c r="N86">
-        <v>1.58</v>
+        <v>29.37</v>
       </c>
       <c r="O86">
-        <v>1.49</v>
+        <v>30.22</v>
       </c>
     </row>
     <row r="87" spans="1:15">
@@ -5936,37 +5936,37 @@
         <v>552</v>
       </c>
       <c r="C87">
-        <v>49.14</v>
+        <v>1.51</v>
       </c>
       <c r="D87">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="E87">
-        <v>-36.17</v>
+        <v>-55.75</v>
       </c>
       <c r="F87">
-        <v>73.38</v>
+        <v>46.86</v>
       </c>
       <c r="G87">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="J87">
-        <v>39.1</v>
+        <v>1.63</v>
       </c>
       <c r="K87">
-        <v>41.37</v>
+        <v>1.6</v>
       </c>
       <c r="L87">
-        <v>40.13</v>
+        <v>1.58</v>
       </c>
       <c r="M87">
-        <v>40.4</v>
+        <v>1.62</v>
       </c>
       <c r="N87">
-        <v>41.8</v>
+        <v>1.58</v>
       </c>
       <c r="O87">
-        <v>42.5</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="88" spans="1:15">
@@ -5977,37 +5977,37 @@
         <v>552</v>
       </c>
       <c r="C88">
-        <v>50.75</v>
+        <v>49.14</v>
       </c>
       <c r="D88">
-        <v>4</v>
+        <v>1.36</v>
       </c>
       <c r="E88">
-        <v>35.11</v>
+        <v>-36.17</v>
       </c>
       <c r="F88">
-        <v>64.69</v>
+        <v>73.38</v>
       </c>
       <c r="G88">
-        <v>0.47</v>
+        <v>1.22</v>
       </c>
       <c r="J88">
-        <v>46.95</v>
+        <v>39.1</v>
       </c>
       <c r="K88">
-        <v>46.51</v>
+        <v>41.37</v>
       </c>
       <c r="L88">
-        <v>46.53</v>
+        <v>40.13</v>
       </c>
       <c r="M88">
-        <v>46.8</v>
+        <v>40.4</v>
       </c>
       <c r="N88">
-        <v>46.12</v>
+        <v>41.8</v>
       </c>
       <c r="O88">
-        <v>46.77</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="89" spans="1:15">
@@ -6018,37 +6018,37 @@
         <v>552</v>
       </c>
       <c r="C89">
-        <v>17.75</v>
+        <v>50.75</v>
       </c>
       <c r="D89">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E89">
-        <v>-63.5</v>
+        <v>35.11</v>
       </c>
       <c r="F89">
-        <v>43.6</v>
+        <v>64.69</v>
       </c>
       <c r="G89">
-        <v>0.08</v>
+        <v>0.47</v>
       </c>
       <c r="J89">
-        <v>22.45</v>
+        <v>46.95</v>
       </c>
       <c r="K89">
-        <v>22.18</v>
+        <v>46.51</v>
       </c>
       <c r="L89">
-        <v>21.43</v>
+        <v>46.53</v>
       </c>
       <c r="M89">
-        <v>22.51</v>
+        <v>46.8</v>
       </c>
       <c r="N89">
-        <v>22.07</v>
+        <v>46.12</v>
       </c>
       <c r="O89">
-        <v>18.11</v>
+        <v>46.77</v>
       </c>
     </row>
     <row r="90" spans="1:15">
@@ -6059,43 +6059,37 @@
         <v>552</v>
       </c>
       <c r="C90">
-        <v>85.2</v>
+        <v>17.75</v>
       </c>
       <c r="D90">
-        <v>-0.41</v>
+        <v>-1</v>
       </c>
       <c r="E90">
-        <v>19.51</v>
+        <v>-63.5</v>
       </c>
       <c r="F90">
-        <v>48.63</v>
+        <v>43.6</v>
       </c>
       <c r="G90">
-        <v>1.56</v>
-      </c>
-      <c r="H90" t="s">
-        <v>561</v>
-      </c>
-      <c r="I90" t="s">
-        <v>617</v>
+        <v>0.08</v>
       </c>
       <c r="J90">
-        <v>92.16</v>
+        <v>22.45</v>
       </c>
       <c r="K90">
-        <v>89.98999999999999</v>
+        <v>22.18</v>
       </c>
       <c r="L90">
-        <v>83.04000000000001</v>
+        <v>21.43</v>
       </c>
       <c r="M90">
-        <v>91.67</v>
+        <v>22.51</v>
       </c>
       <c r="N90">
-        <v>88.69</v>
+        <v>22.07</v>
       </c>
       <c r="O90">
-        <v>79.52</v>
+        <v>18.11</v>
       </c>
     </row>
     <row r="91" spans="1:15">
@@ -6106,37 +6100,43 @@
         <v>552</v>
       </c>
       <c r="C91">
-        <v>6.25</v>
+        <v>85.2</v>
       </c>
       <c r="D91">
-        <v>-0.48</v>
+        <v>-0.41</v>
       </c>
       <c r="E91">
-        <v>-75.08</v>
+        <v>19.51</v>
       </c>
       <c r="F91">
-        <v>39.97</v>
+        <v>48.63</v>
       </c>
       <c r="G91">
-        <v>-0.02</v>
+        <v>1.56</v>
+      </c>
+      <c r="H91" t="s">
+        <v>561</v>
+      </c>
+      <c r="I91" t="s">
+        <v>617</v>
       </c>
       <c r="J91">
-        <v>6.67</v>
+        <v>92.16</v>
       </c>
       <c r="K91">
-        <v>6.69</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="L91">
-        <v>6.48</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="M91">
-        <v>6.67</v>
+        <v>91.67</v>
       </c>
       <c r="N91">
-        <v>6.69</v>
+        <v>88.69</v>
       </c>
       <c r="O91">
-        <v>6.69</v>
+        <v>79.52</v>
       </c>
     </row>
     <row r="92" spans="1:15">
@@ -6147,37 +6147,37 @@
         <v>552</v>
       </c>
       <c r="C92">
-        <v>19.2</v>
+        <v>6.25</v>
       </c>
       <c r="D92">
-        <v>-2.04</v>
+        <v>-0.48</v>
       </c>
       <c r="E92">
-        <v>5.05</v>
+        <v>-75.08</v>
       </c>
       <c r="F92">
-        <v>38.09</v>
+        <v>39.97</v>
       </c>
       <c r="G92">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="J92">
-        <v>21.36</v>
+        <v>6.67</v>
       </c>
       <c r="K92">
-        <v>21.81</v>
+        <v>6.69</v>
       </c>
       <c r="L92">
-        <v>21.53</v>
+        <v>6.48</v>
       </c>
       <c r="M92">
-        <v>20.96</v>
+        <v>6.67</v>
       </c>
       <c r="N92">
-        <v>21.52</v>
+        <v>6.69</v>
       </c>
       <c r="O92">
-        <v>21.92</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="93" spans="1:15">
@@ -6188,43 +6188,37 @@
         <v>552</v>
       </c>
       <c r="C93">
-        <v>6.01</v>
+        <v>19.2</v>
       </c>
       <c r="D93">
-        <v>-0.99</v>
+        <v>-2.04</v>
       </c>
       <c r="E93">
-        <v>-47.8</v>
+        <v>5.05</v>
       </c>
       <c r="F93">
-        <v>45.41</v>
+        <v>38.09</v>
       </c>
       <c r="G93">
-        <v>0.01</v>
-      </c>
-      <c r="H93" t="s">
-        <v>553</v>
-      </c>
-      <c r="I93" t="s">
-        <v>616</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J93">
-        <v>6.45</v>
+        <v>21.36</v>
       </c>
       <c r="K93">
-        <v>6.36</v>
+        <v>21.81</v>
       </c>
       <c r="L93">
-        <v>6.3</v>
+        <v>21.53</v>
       </c>
       <c r="M93">
-        <v>6.45</v>
+        <v>20.96</v>
       </c>
       <c r="N93">
-        <v>6.33</v>
+        <v>21.52</v>
       </c>
       <c r="O93">
-        <v>6.03</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="94" spans="1:15">
@@ -6235,37 +6229,43 @@
         <v>552</v>
       </c>
       <c r="C94">
-        <v>6.29</v>
+        <v>6.01</v>
       </c>
       <c r="D94">
-        <v>-0.47</v>
+        <v>-0.99</v>
       </c>
       <c r="E94">
-        <v>-64.84999999999999</v>
+        <v>-47.8</v>
       </c>
       <c r="F94">
-        <v>40.67</v>
+        <v>45.41</v>
       </c>
       <c r="G94">
-        <v>-0.02</v>
+        <v>0.01</v>
+      </c>
+      <c r="H94" t="s">
+        <v>553</v>
+      </c>
+      <c r="I94" t="s">
+        <v>616</v>
       </c>
       <c r="J94">
-        <v>6.98</v>
+        <v>6.45</v>
       </c>
       <c r="K94">
-        <v>6.78</v>
+        <v>6.36</v>
       </c>
       <c r="L94">
-        <v>6.76</v>
+        <v>6.3</v>
       </c>
       <c r="M94">
-        <v>7.04</v>
+        <v>6.45</v>
       </c>
       <c r="N94">
-        <v>6.77</v>
+        <v>6.33</v>
       </c>
       <c r="O94">
-        <v>6.79</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="95" spans="1:15">
@@ -6276,37 +6276,37 @@
         <v>552</v>
       </c>
       <c r="C95">
-        <v>84.8</v>
+        <v>6.29</v>
       </c>
       <c r="D95">
-        <v>-0.93</v>
+        <v>-0.47</v>
       </c>
       <c r="E95">
-        <v>-86.33</v>
+        <v>-64.84999999999999</v>
       </c>
       <c r="F95">
-        <v>40.33</v>
+        <v>40.67</v>
       </c>
       <c r="G95">
-        <v>-0.36</v>
+        <v>-0.02</v>
       </c>
       <c r="J95">
-        <v>86.94</v>
+        <v>6.98</v>
       </c>
       <c r="K95">
-        <v>88.42</v>
+        <v>6.78</v>
       </c>
       <c r="L95">
-        <v>91.23</v>
+        <v>6.76</v>
       </c>
       <c r="M95">
-        <v>86.34999999999999</v>
+        <v>7.04</v>
       </c>
       <c r="N95">
-        <v>88</v>
+        <v>6.77</v>
       </c>
       <c r="O95">
-        <v>87.91</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="96" spans="1:15">
@@ -6317,37 +6317,37 @@
         <v>552</v>
       </c>
       <c r="C96">
-        <v>14.4</v>
+        <v>84.8</v>
       </c>
       <c r="D96">
-        <v>1.41</v>
+        <v>-0.93</v>
       </c>
       <c r="E96">
-        <v>23.42</v>
+        <v>-86.33</v>
       </c>
       <c r="F96">
-        <v>52.65</v>
+        <v>40.33</v>
       </c>
       <c r="G96">
-        <v>-0.23</v>
+        <v>-0.36</v>
       </c>
       <c r="J96">
-        <v>12.65</v>
+        <v>86.94</v>
       </c>
       <c r="K96">
-        <v>15.07</v>
+        <v>88.42</v>
       </c>
       <c r="L96">
-        <v>15.38</v>
+        <v>91.23</v>
       </c>
       <c r="M96">
-        <v>11.37</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="N96">
-        <v>12.98</v>
+        <v>88</v>
       </c>
       <c r="O96">
-        <v>15.21</v>
+        <v>87.91</v>
       </c>
     </row>
     <row r="97" spans="1:15">
@@ -6358,37 +6358,37 @@
         <v>552</v>
       </c>
       <c r="C97">
-        <v>9.25</v>
+        <v>14.4</v>
       </c>
       <c r="D97">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="E97">
-        <v>-65.42</v>
+        <v>23.42</v>
       </c>
       <c r="F97">
-        <v>57.89</v>
+        <v>52.65</v>
       </c>
       <c r="G97">
-        <v>0.01</v>
+        <v>-0.23</v>
       </c>
       <c r="J97">
-        <v>8.33</v>
+        <v>12.65</v>
       </c>
       <c r="K97">
-        <v>8.539999999999999</v>
+        <v>15.07</v>
       </c>
       <c r="L97">
-        <v>8.98</v>
+        <v>15.38</v>
       </c>
       <c r="M97">
-        <v>8.43</v>
+        <v>11.37</v>
       </c>
       <c r="N97">
-        <v>8.640000000000001</v>
+        <v>12.98</v>
       </c>
       <c r="O97">
-        <v>8.99</v>
+        <v>15.21</v>
       </c>
     </row>
     <row r="98" spans="1:15">
@@ -6399,37 +6399,37 @@
         <v>552</v>
       </c>
       <c r="C98">
-        <v>89.2</v>
+        <v>9.25</v>
       </c>
       <c r="D98">
-        <v>0.06</v>
+        <v>1.31</v>
       </c>
       <c r="E98">
-        <v>-74.92</v>
+        <v>-65.42</v>
       </c>
       <c r="F98">
-        <v>40.05</v>
+        <v>57.89</v>
       </c>
       <c r="G98">
-        <v>0.38</v>
+        <v>0.01</v>
       </c>
       <c r="J98">
-        <v>107.75</v>
+        <v>8.33</v>
       </c>
       <c r="K98">
-        <v>109.94</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="L98">
-        <v>103.4</v>
+        <v>8.98</v>
       </c>
       <c r="M98">
-        <v>109.53</v>
+        <v>8.43</v>
       </c>
       <c r="N98">
-        <v>106.89</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="O98">
-        <v>90.09999999999999</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="99" spans="1:15">
@@ -6440,43 +6440,37 @@
         <v>552</v>
       </c>
       <c r="C99">
-        <v>15.6</v>
+        <v>89.2</v>
       </c>
       <c r="D99">
-        <v>-8.02</v>
+        <v>0.06</v>
       </c>
       <c r="E99">
-        <v>2.49</v>
+        <v>-74.92</v>
       </c>
       <c r="F99">
-        <v>47.14</v>
+        <v>40.05</v>
       </c>
       <c r="G99">
-        <v>-0.02</v>
-      </c>
-      <c r="H99" t="s">
-        <v>570</v>
-      </c>
-      <c r="I99" t="s">
-        <v>621</v>
+        <v>0.38</v>
       </c>
       <c r="J99">
-        <v>16.45</v>
+        <v>107.75</v>
       </c>
       <c r="K99">
-        <v>16.44</v>
+        <v>109.94</v>
       </c>
       <c r="L99">
-        <v>16.27</v>
+        <v>103.4</v>
       </c>
       <c r="M99">
-        <v>15.86</v>
+        <v>109.53</v>
       </c>
       <c r="N99">
-        <v>16.43</v>
+        <v>106.89</v>
       </c>
       <c r="O99">
-        <v>16.35</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="100" spans="1:15">
@@ -6487,37 +6481,43 @@
         <v>552</v>
       </c>
       <c r="C100">
-        <v>496.25</v>
+        <v>15.6</v>
       </c>
       <c r="D100">
-        <v>-0.75</v>
+        <v>-8.02</v>
       </c>
       <c r="E100">
-        <v>-20.32</v>
+        <v>2.49</v>
       </c>
       <c r="F100">
-        <v>34.72</v>
+        <v>47.14</v>
       </c>
       <c r="G100">
-        <v>-5.66</v>
+        <v>-0.02</v>
+      </c>
+      <c r="H100" t="s">
+        <v>570</v>
+      </c>
+      <c r="I100" t="s">
+        <v>621</v>
       </c>
       <c r="J100">
-        <v>582.37</v>
+        <v>16.45</v>
       </c>
       <c r="K100">
-        <v>634.11</v>
+        <v>16.44</v>
       </c>
       <c r="L100">
-        <v>623.61</v>
+        <v>16.27</v>
       </c>
       <c r="M100">
-        <v>563.27</v>
+        <v>15.86</v>
       </c>
       <c r="N100">
-        <v>598.33</v>
+        <v>16.43</v>
       </c>
       <c r="O100">
-        <v>632.47</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="101" spans="1:15">
@@ -6528,37 +6528,37 @@
         <v>552</v>
       </c>
       <c r="C101">
-        <v>2219</v>
+        <v>496.25</v>
       </c>
       <c r="D101">
-        <v>-0.9399999999999999</v>
+        <v>-0.75</v>
       </c>
       <c r="E101">
-        <v>-0.42</v>
+        <v>-20.32</v>
       </c>
       <c r="F101">
-        <v>44.64</v>
+        <v>34.72</v>
       </c>
       <c r="G101">
-        <v>-4.9</v>
+        <v>-5.66</v>
       </c>
       <c r="J101">
-        <v>2328.11</v>
+        <v>582.37</v>
       </c>
       <c r="K101">
-        <v>2343.28</v>
+        <v>634.11</v>
       </c>
       <c r="L101">
-        <v>2285.42</v>
+        <v>623.61</v>
       </c>
       <c r="M101">
-        <v>2332.38</v>
+        <v>563.27</v>
       </c>
       <c r="N101">
-        <v>2340.08</v>
+        <v>598.33</v>
       </c>
       <c r="O101">
-        <v>2338.04</v>
+        <v>632.47</v>
       </c>
     </row>
     <row r="102" spans="1:15">
@@ -6569,37 +6569,37 @@
         <v>552</v>
       </c>
       <c r="C102">
-        <v>32.98</v>
+        <v>2219</v>
       </c>
       <c r="D102">
-        <v>-0.66</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E102">
-        <v>-79.2</v>
+        <v>-0.42</v>
       </c>
       <c r="F102">
-        <v>63.14</v>
+        <v>44.64</v>
       </c>
       <c r="G102">
-        <v>-0.04</v>
+        <v>-4.9</v>
       </c>
       <c r="J102">
-        <v>25.14</v>
+        <v>2328.11</v>
       </c>
       <c r="K102">
-        <v>30.71</v>
+        <v>2343.28</v>
       </c>
       <c r="L102">
-        <v>33.62</v>
+        <v>2285.42</v>
       </c>
       <c r="M102">
-        <v>23.41</v>
+        <v>2332.38</v>
       </c>
       <c r="N102">
-        <v>26.48</v>
+        <v>2340.08</v>
       </c>
       <c r="O102">
-        <v>32.51</v>
+        <v>2338.04</v>
       </c>
     </row>
     <row r="103" spans="1:15">
@@ -6610,37 +6610,37 @@
         <v>552</v>
       </c>
       <c r="C103">
-        <v>6.8</v>
+        <v>32.98</v>
       </c>
       <c r="D103">
-        <v>-1.02</v>
+        <v>-0.66</v>
       </c>
       <c r="E103">
-        <v>-72.48999999999999</v>
+        <v>-79.2</v>
       </c>
       <c r="F103">
-        <v>78.66</v>
+        <v>63.14</v>
       </c>
       <c r="G103">
-        <v>0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="J103">
-        <v>4.85</v>
+        <v>25.14</v>
       </c>
       <c r="K103">
-        <v>5.42</v>
+        <v>30.71</v>
       </c>
       <c r="L103">
-        <v>5.87</v>
+        <v>33.62</v>
       </c>
       <c r="M103">
-        <v>4.7</v>
+        <v>23.41</v>
       </c>
       <c r="N103">
-        <v>5</v>
+        <v>26.48</v>
       </c>
       <c r="O103">
-        <v>5.46</v>
+        <v>32.51</v>
       </c>
     </row>
     <row r="104" spans="1:15">
@@ -6651,43 +6651,37 @@
         <v>552</v>
       </c>
       <c r="C104">
-        <v>6.13</v>
+        <v>6.8</v>
       </c>
       <c r="D104">
-        <v>-0.49</v>
+        <v>-1.02</v>
       </c>
       <c r="E104">
-        <v>-52.01</v>
+        <v>-72.48999999999999</v>
       </c>
       <c r="F104">
-        <v>34.88</v>
+        <v>78.66</v>
       </c>
       <c r="G104">
-        <v>0.01</v>
-      </c>
-      <c r="H104" t="s">
-        <v>553</v>
-      </c>
-      <c r="I104" t="s">
-        <v>616</v>
+        <v>0.12</v>
       </c>
       <c r="J104">
-        <v>6.85</v>
+        <v>4.85</v>
       </c>
       <c r="K104">
-        <v>6.92</v>
+        <v>5.42</v>
       </c>
       <c r="L104">
-        <v>6.58</v>
+        <v>5.87</v>
       </c>
       <c r="M104">
-        <v>6.91</v>
+        <v>4.7</v>
       </c>
       <c r="N104">
-        <v>6.71</v>
+        <v>5</v>
       </c>
       <c r="O104">
-        <v>6.16</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="105" spans="1:15">
@@ -6698,37 +6692,43 @@
         <v>552</v>
       </c>
       <c r="C105">
-        <v>44.3</v>
+        <v>6.13</v>
       </c>
       <c r="D105">
-        <v>4.68</v>
+        <v>-0.49</v>
       </c>
       <c r="E105">
-        <v>-44.6</v>
+        <v>-52.01</v>
       </c>
       <c r="F105">
-        <v>50.51</v>
+        <v>34.88</v>
       </c>
       <c r="G105">
-        <v>-0.03</v>
+        <v>0.01</v>
+      </c>
+      <c r="H105" t="s">
+        <v>553</v>
+      </c>
+      <c r="I105" t="s">
+        <v>616</v>
       </c>
       <c r="J105">
-        <v>46.29</v>
+        <v>6.85</v>
       </c>
       <c r="K105">
-        <v>46.75</v>
+        <v>6.92</v>
       </c>
       <c r="L105">
-        <v>46</v>
+        <v>6.58</v>
       </c>
       <c r="M105">
-        <v>45.63</v>
+        <v>6.91</v>
       </c>
       <c r="N105">
-        <v>46.36</v>
+        <v>6.71</v>
       </c>
       <c r="O105">
-        <v>46.73</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="106" spans="1:15">
@@ -6739,37 +6739,37 @@
         <v>552</v>
       </c>
       <c r="C106">
-        <v>38.48</v>
+        <v>44.3</v>
       </c>
       <c r="D106">
-        <v>0.58</v>
+        <v>4.68</v>
       </c>
       <c r="E106">
-        <v>-67.41</v>
+        <v>-44.6</v>
       </c>
       <c r="F106">
-        <v>32.65</v>
+        <v>50.51</v>
       </c>
       <c r="G106">
-        <v>-0.98</v>
+        <v>-0.03</v>
       </c>
       <c r="J106">
-        <v>57.14</v>
+        <v>46.29</v>
       </c>
       <c r="K106">
-        <v>56.36</v>
+        <v>46.75</v>
       </c>
       <c r="L106">
-        <v>48.92</v>
+        <v>46</v>
       </c>
       <c r="M106">
-        <v>57.17</v>
+        <v>45.63</v>
       </c>
       <c r="N106">
-        <v>53.07</v>
+        <v>46.36</v>
       </c>
       <c r="O106">
-        <v>45.19</v>
+        <v>46.73</v>
       </c>
     </row>
     <row r="107" spans="1:15">
@@ -6780,37 +6780,37 @@
         <v>552</v>
       </c>
       <c r="C107">
-        <v>795</v>
+        <v>38.48</v>
       </c>
       <c r="D107">
-        <v>2.58</v>
+        <v>0.58</v>
       </c>
       <c r="E107">
-        <v>-78.09999999999999</v>
+        <v>-67.41</v>
       </c>
       <c r="F107">
-        <v>51.85</v>
+        <v>32.65</v>
       </c>
       <c r="G107">
-        <v>-12.34</v>
+        <v>-0.98</v>
       </c>
       <c r="J107">
-        <v>717.29</v>
+        <v>57.14</v>
       </c>
       <c r="K107">
-        <v>804.9299999999999</v>
+        <v>56.36</v>
       </c>
       <c r="L107">
-        <v>844.17</v>
+        <v>48.92</v>
       </c>
       <c r="M107">
-        <v>657.64</v>
+        <v>57.17</v>
       </c>
       <c r="N107">
-        <v>757.46</v>
+        <v>53.07</v>
       </c>
       <c r="O107">
-        <v>844.4400000000001</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="108" spans="1:15">
@@ -6821,37 +6821,37 @@
         <v>552</v>
       </c>
       <c r="C108">
-        <v>105.9</v>
+        <v>795</v>
       </c>
       <c r="D108">
-        <v>0.09</v>
+        <v>2.58</v>
       </c>
       <c r="E108">
-        <v>-60.79</v>
+        <v>-78.09999999999999</v>
       </c>
       <c r="F108">
-        <v>44.57</v>
+        <v>51.85</v>
       </c>
       <c r="G108">
-        <v>-0.15</v>
+        <v>-12.34</v>
       </c>
       <c r="J108">
-        <v>116.31</v>
+        <v>717.29</v>
       </c>
       <c r="K108">
-        <v>111.67</v>
+        <v>804.9299999999999</v>
       </c>
       <c r="L108">
-        <v>109.4</v>
+        <v>844.17</v>
       </c>
       <c r="M108">
-        <v>111.91</v>
+        <v>657.64</v>
       </c>
       <c r="N108">
-        <v>113.06</v>
+        <v>757.46</v>
       </c>
       <c r="O108">
-        <v>107.96</v>
+        <v>844.4400000000001</v>
       </c>
     </row>
     <row r="109" spans="1:15">
@@ -6862,37 +6862,37 @@
         <v>552</v>
       </c>
       <c r="C109">
-        <v>33.38</v>
+        <v>105.9</v>
       </c>
       <c r="D109">
-        <v>0.54</v>
+        <v>0.09</v>
       </c>
       <c r="E109">
-        <v>-21.41</v>
+        <v>-60.79</v>
       </c>
       <c r="F109">
-        <v>45.95</v>
+        <v>44.57</v>
       </c>
       <c r="G109">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="J109">
-        <v>35.16</v>
+        <v>116.31</v>
       </c>
       <c r="K109">
-        <v>35.42</v>
+        <v>111.67</v>
       </c>
       <c r="L109">
-        <v>34.84</v>
+        <v>109.4</v>
       </c>
       <c r="M109">
-        <v>33.44</v>
+        <v>111.91</v>
       </c>
       <c r="N109">
-        <v>35.86</v>
+        <v>113.06</v>
       </c>
       <c r="O109">
-        <v>34.69</v>
+        <v>107.96</v>
       </c>
     </row>
     <row r="110" spans="1:15">
@@ -6903,43 +6903,37 @@
         <v>552</v>
       </c>
       <c r="C110">
-        <v>1.57</v>
+        <v>33.38</v>
       </c>
       <c r="D110">
-        <v>1.95</v>
+        <v>0.54</v>
       </c>
       <c r="E110">
-        <v>-23.26</v>
+        <v>-21.41</v>
       </c>
       <c r="F110">
-        <v>45.53</v>
+        <v>45.95</v>
       </c>
       <c r="G110">
-        <v>0.01</v>
-      </c>
-      <c r="H110" t="s">
-        <v>558</v>
-      </c>
-      <c r="I110" t="s">
-        <v>618</v>
+        <v>-0.16</v>
       </c>
       <c r="J110">
-        <v>1.82</v>
+        <v>35.16</v>
       </c>
       <c r="K110">
-        <v>1.76</v>
+        <v>35.42</v>
       </c>
       <c r="L110">
-        <v>1.75</v>
+        <v>34.84</v>
       </c>
       <c r="M110">
-        <v>1.76</v>
+        <v>33.44</v>
       </c>
       <c r="N110">
-        <v>1.75</v>
+        <v>35.86</v>
       </c>
       <c r="O110">
-        <v>1.54</v>
+        <v>34.69</v>
       </c>
     </row>
     <row r="111" spans="1:15">
@@ -6950,37 +6944,43 @@
         <v>552</v>
       </c>
       <c r="C111">
-        <v>93.84999999999999</v>
+        <v>1.57</v>
       </c>
       <c r="D111">
-        <v>-1.21</v>
+        <v>1.95</v>
       </c>
       <c r="E111">
-        <v>-72.17</v>
+        <v>-23.26</v>
       </c>
       <c r="F111">
-        <v>35.06</v>
+        <v>45.53</v>
       </c>
       <c r="G111">
-        <v>-0.33</v>
+        <v>0.01</v>
+      </c>
+      <c r="H111" t="s">
+        <v>558</v>
+      </c>
+      <c r="I111" t="s">
+        <v>618</v>
       </c>
       <c r="J111">
-        <v>104.16</v>
+        <v>1.82</v>
       </c>
       <c r="K111">
-        <v>99.47</v>
+        <v>1.76</v>
       </c>
       <c r="L111">
-        <v>98.59999999999999</v>
+        <v>1.75</v>
       </c>
       <c r="M111">
-        <v>104.71</v>
+        <v>1.76</v>
       </c>
       <c r="N111">
-        <v>99.75</v>
+        <v>1.75</v>
       </c>
       <c r="O111">
-        <v>98.58</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="112" spans="1:15">
@@ -6991,43 +6991,37 @@
         <v>552</v>
       </c>
       <c r="C112">
-        <v>48.78</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="D112">
-        <v>8.16</v>
+        <v>-1.21</v>
       </c>
       <c r="E112">
-        <v>-28.23</v>
+        <v>-72.17</v>
       </c>
       <c r="F112">
-        <v>62.64</v>
+        <v>35.06</v>
       </c>
       <c r="G112">
-        <v>0.54</v>
-      </c>
-      <c r="H112" t="s">
-        <v>558</v>
-      </c>
-      <c r="I112" t="s">
-        <v>618</v>
+        <v>-0.33</v>
       </c>
       <c r="J112">
-        <v>40.83</v>
+        <v>104.16</v>
       </c>
       <c r="K112">
-        <v>41.82</v>
+        <v>99.47</v>
       </c>
       <c r="L112">
-        <v>44.49</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M112">
-        <v>41.14</v>
+        <v>104.71</v>
       </c>
       <c r="N112">
-        <v>42.71</v>
+        <v>99.75</v>
       </c>
       <c r="O112">
-        <v>45.78</v>
+        <v>98.58</v>
       </c>
     </row>
     <row r="113" spans="1:15">
@@ -7038,37 +7032,43 @@
         <v>552</v>
       </c>
       <c r="C113">
-        <v>71.5</v>
+        <v>48.78</v>
       </c>
       <c r="D113">
-        <v>0.21</v>
+        <v>8.16</v>
       </c>
       <c r="E113">
-        <v>15.23</v>
+        <v>-28.23</v>
       </c>
       <c r="F113">
-        <v>50.95</v>
+        <v>62.64</v>
       </c>
       <c r="G113">
-        <v>0.01</v>
+        <v>0.54</v>
+      </c>
+      <c r="H113" t="s">
+        <v>558</v>
+      </c>
+      <c r="I113" t="s">
+        <v>618</v>
       </c>
       <c r="J113">
-        <v>69.55</v>
+        <v>40.83</v>
       </c>
       <c r="K113">
-        <v>73.05</v>
+        <v>41.82</v>
       </c>
       <c r="L113">
-        <v>71.91</v>
+        <v>44.49</v>
       </c>
       <c r="M113">
-        <v>70.3</v>
+        <v>41.14</v>
       </c>
       <c r="N113">
-        <v>72.91</v>
+        <v>42.71</v>
       </c>
       <c r="O113">
-        <v>70.28</v>
+        <v>45.78</v>
       </c>
     </row>
     <row r="114" spans="1:15">
@@ -7079,37 +7079,37 @@
         <v>552</v>
       </c>
       <c r="C114">
-        <v>9.76</v>
+        <v>71.5</v>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="E114">
-        <v>-78.31999999999999</v>
+        <v>15.23</v>
       </c>
       <c r="F114">
-        <v>41.34</v>
+        <v>50.95</v>
       </c>
       <c r="G114">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="J114">
-        <v>10.91</v>
+        <v>69.55</v>
       </c>
       <c r="K114">
-        <v>10.7</v>
+        <v>73.05</v>
       </c>
       <c r="L114">
-        <v>10.38</v>
+        <v>71.91</v>
       </c>
       <c r="M114">
-        <v>10.89</v>
+        <v>70.3</v>
       </c>
       <c r="N114">
-        <v>10.93</v>
+        <v>72.91</v>
       </c>
       <c r="O114">
-        <v>10.52</v>
+        <v>70.28</v>
       </c>
     </row>
     <row r="115" spans="1:15">
@@ -7120,37 +7120,37 @@
         <v>552</v>
       </c>
       <c r="C115">
-        <v>4.57</v>
+        <v>9.76</v>
       </c>
       <c r="D115">
-        <v>-0.65</v>
+        <v>0</v>
       </c>
       <c r="E115">
-        <v>-53.07</v>
+        <v>-78.31999999999999</v>
       </c>
       <c r="F115">
-        <v>39.66</v>
+        <v>41.34</v>
       </c>
       <c r="G115">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="J115">
-        <v>5.25</v>
+        <v>10.91</v>
       </c>
       <c r="K115">
-        <v>5.25</v>
+        <v>10.7</v>
       </c>
       <c r="L115">
-        <v>5.45</v>
+        <v>10.38</v>
       </c>
       <c r="M115">
-        <v>5.27</v>
+        <v>10.89</v>
       </c>
       <c r="N115">
-        <v>5.24</v>
+        <v>10.93</v>
       </c>
       <c r="O115">
-        <v>5.39</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="116" spans="1:15">
@@ -7161,37 +7161,37 @@
         <v>552</v>
       </c>
       <c r="C116">
-        <v>10.46</v>
+        <v>4.57</v>
       </c>
       <c r="D116">
-        <v>0.77</v>
+        <v>-0.65</v>
       </c>
       <c r="E116">
-        <v>-66.79000000000001</v>
+        <v>-53.07</v>
       </c>
       <c r="F116">
-        <v>37.21</v>
+        <v>39.66</v>
       </c>
       <c r="G116">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="J116">
-        <v>11.51</v>
+        <v>5.25</v>
       </c>
       <c r="K116">
-        <v>11.82</v>
+        <v>5.25</v>
       </c>
       <c r="L116">
-        <v>11.32</v>
+        <v>5.45</v>
       </c>
       <c r="M116">
-        <v>11.66</v>
+        <v>5.27</v>
       </c>
       <c r="N116">
-        <v>11.84</v>
+        <v>5.24</v>
       </c>
       <c r="O116">
-        <v>10.48</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="117" spans="1:15">
@@ -7202,37 +7202,37 @@
         <v>552</v>
       </c>
       <c r="C117">
-        <v>63.2</v>
+        <v>10.46</v>
       </c>
       <c r="D117">
-        <v>0.32</v>
+        <v>0.77</v>
       </c>
       <c r="E117">
-        <v>-65.77</v>
+        <v>-66.79000000000001</v>
       </c>
       <c r="F117">
-        <v>61.76</v>
+        <v>37.21</v>
       </c>
       <c r="G117">
-        <v>1.06</v>
+        <v>0.01</v>
       </c>
       <c r="J117">
-        <v>57.4</v>
+        <v>11.51</v>
       </c>
       <c r="K117">
-        <v>59.19</v>
+        <v>11.82</v>
       </c>
       <c r="L117">
-        <v>57.71</v>
+        <v>11.32</v>
       </c>
       <c r="M117">
-        <v>57.92</v>
+        <v>11.66</v>
       </c>
       <c r="N117">
-        <v>59.13</v>
+        <v>11.84</v>
       </c>
       <c r="O117">
-        <v>58.17</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="118" spans="1:15">
@@ -7243,37 +7243,37 @@
         <v>552</v>
       </c>
       <c r="C118">
-        <v>21.6</v>
+        <v>63.2</v>
       </c>
       <c r="D118">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="E118">
-        <v>-81.95999999999999</v>
+        <v>-65.77</v>
       </c>
       <c r="F118">
-        <v>51.18</v>
+        <v>61.76</v>
       </c>
       <c r="G118">
-        <v>0.17</v>
+        <v>1.06</v>
       </c>
       <c r="J118">
-        <v>23.95</v>
+        <v>57.4</v>
       </c>
       <c r="K118">
-        <v>22.38</v>
+        <v>59.19</v>
       </c>
       <c r="L118">
-        <v>22.01</v>
+        <v>57.71</v>
       </c>
       <c r="M118">
-        <v>22.41</v>
+        <v>57.92</v>
       </c>
       <c r="N118">
-        <v>22.12</v>
+        <v>59.13</v>
       </c>
       <c r="O118">
-        <v>21.13</v>
+        <v>58.17</v>
       </c>
     </row>
     <row r="119" spans="1:15">
@@ -7284,37 +7284,37 @@
         <v>552</v>
       </c>
       <c r="C119">
-        <v>35.98</v>
+        <v>21.6</v>
       </c>
       <c r="D119">
-        <v>-0.11</v>
+        <v>0.37</v>
       </c>
       <c r="E119">
-        <v>-44.85</v>
+        <v>-81.95999999999999</v>
       </c>
       <c r="F119">
-        <v>45.63</v>
+        <v>51.18</v>
       </c>
       <c r="G119">
-        <v>-0.05</v>
+        <v>0.17</v>
       </c>
       <c r="J119">
-        <v>36.73</v>
+        <v>23.95</v>
       </c>
       <c r="K119">
-        <v>37.56</v>
+        <v>22.38</v>
       </c>
       <c r="L119">
-        <v>37.86</v>
+        <v>22.01</v>
       </c>
       <c r="M119">
-        <v>37.16</v>
+        <v>22.41</v>
       </c>
       <c r="N119">
-        <v>38.22</v>
+        <v>22.12</v>
       </c>
       <c r="O119">
-        <v>36.73</v>
+        <v>21.13</v>
       </c>
     </row>
     <row r="120" spans="1:15">
@@ -7325,43 +7325,37 @@
         <v>552</v>
       </c>
       <c r="C120">
-        <v>49.9</v>
+        <v>35.98</v>
       </c>
       <c r="D120">
-        <v>2.67</v>
+        <v>-0.11</v>
       </c>
       <c r="E120">
-        <v>-64.88</v>
+        <v>-44.85</v>
       </c>
       <c r="F120">
-        <v>50.05</v>
+        <v>45.63</v>
       </c>
       <c r="G120">
-        <v>-0.01</v>
-      </c>
-      <c r="H120" t="s">
-        <v>571</v>
-      </c>
-      <c r="I120" t="s">
-        <v>620</v>
+        <v>-0.05</v>
       </c>
       <c r="J120">
-        <v>48.62</v>
+        <v>36.73</v>
       </c>
       <c r="K120">
-        <v>49.62</v>
+        <v>37.56</v>
       </c>
       <c r="L120">
-        <v>51.29</v>
+        <v>37.86</v>
       </c>
       <c r="M120">
-        <v>48.25</v>
+        <v>37.16</v>
       </c>
       <c r="N120">
-        <v>48.87</v>
+        <v>38.22</v>
       </c>
       <c r="O120">
-        <v>49.95</v>
+        <v>36.73</v>
       </c>
     </row>
     <row r="121" spans="1:15">
@@ -7372,43 +7366,43 @@
         <v>552</v>
       </c>
       <c r="C121">
-        <v>1829</v>
+        <v>49.9</v>
       </c>
       <c r="D121">
-        <v>2.29</v>
+        <v>2.67</v>
       </c>
       <c r="E121">
-        <v>-66.37</v>
+        <v>-64.88</v>
       </c>
       <c r="F121">
-        <v>54.11</v>
+        <v>50.05</v>
       </c>
       <c r="G121">
-        <v>5.81</v>
+        <v>-0.01</v>
       </c>
       <c r="H121" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I121" t="s">
         <v>620</v>
       </c>
       <c r="J121">
-        <v>1742.27</v>
+        <v>48.62</v>
       </c>
       <c r="K121">
-        <v>1805.34</v>
+        <v>49.62</v>
       </c>
       <c r="L121">
-        <v>1811.45</v>
+        <v>51.29</v>
       </c>
       <c r="M121">
-        <v>1781.21</v>
+        <v>48.25</v>
       </c>
       <c r="N121">
-        <v>1824.06</v>
+        <v>48.87</v>
       </c>
       <c r="O121">
-        <v>1760.54</v>
+        <v>49.95</v>
       </c>
     </row>
     <row r="122" spans="1:15">
@@ -7419,37 +7413,43 @@
         <v>552</v>
       </c>
       <c r="C122">
-        <v>1721</v>
+        <v>1829</v>
       </c>
       <c r="D122">
-        <v>0.47</v>
+        <v>2.29</v>
       </c>
       <c r="E122">
-        <v>-33.44</v>
+        <v>-66.37</v>
       </c>
       <c r="F122">
-        <v>39.38</v>
+        <v>54.11</v>
       </c>
       <c r="G122">
-        <v>1.02</v>
+        <v>5.81</v>
+      </c>
+      <c r="H122" t="s">
+        <v>572</v>
+      </c>
+      <c r="I122" t="s">
+        <v>620</v>
       </c>
       <c r="J122">
-        <v>1969.36</v>
+        <v>1742.27</v>
       </c>
       <c r="K122">
-        <v>1921.95</v>
+        <v>1805.34</v>
       </c>
       <c r="L122">
-        <v>1916.04</v>
+        <v>1811.45</v>
       </c>
       <c r="M122">
-        <v>1923.03</v>
+        <v>1781.21</v>
       </c>
       <c r="N122">
-        <v>1916.76</v>
+        <v>1824.06</v>
       </c>
       <c r="O122">
-        <v>1724.48</v>
+        <v>1760.54</v>
       </c>
     </row>
     <row r="123" spans="1:15">
@@ -7460,37 +7460,37 @@
         <v>552</v>
       </c>
       <c r="C123">
-        <v>339</v>
+        <v>1721</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="E123">
-        <v>-32.58</v>
+        <v>-33.44</v>
       </c>
       <c r="F123">
-        <v>51</v>
+        <v>39.38</v>
       </c>
       <c r="G123">
-        <v>1.7</v>
+        <v>1.02</v>
       </c>
       <c r="J123">
-        <v>338.97</v>
+        <v>1969.36</v>
       </c>
       <c r="K123">
-        <v>342.51</v>
+        <v>1921.95</v>
       </c>
       <c r="L123">
-        <v>339.4</v>
+        <v>1916.04</v>
       </c>
       <c r="M123">
-        <v>339.87</v>
+        <v>1923.03</v>
       </c>
       <c r="N123">
-        <v>344.36</v>
+        <v>1916.76</v>
       </c>
       <c r="O123">
-        <v>331.98</v>
+        <v>1724.48</v>
       </c>
     </row>
     <row r="124" spans="1:15">
@@ -7501,37 +7501,37 @@
         <v>552</v>
       </c>
       <c r="C124">
-        <v>3.47</v>
+        <v>339</v>
       </c>
       <c r="D124">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="E124">
-        <v>-74.19</v>
+        <v>-32.58</v>
       </c>
       <c r="F124">
-        <v>54.51</v>
+        <v>51</v>
       </c>
       <c r="G124">
-        <v>0.02</v>
+        <v>1.7</v>
       </c>
       <c r="J124">
-        <v>3.29</v>
+        <v>338.97</v>
       </c>
       <c r="K124">
-        <v>3.29</v>
+        <v>342.51</v>
       </c>
       <c r="L124">
-        <v>3.4</v>
+        <v>339.4</v>
       </c>
       <c r="M124">
-        <v>3.29</v>
+        <v>339.87</v>
       </c>
       <c r="N124">
-        <v>3.29</v>
+        <v>344.36</v>
       </c>
       <c r="O124">
-        <v>3.3</v>
+        <v>331.98</v>
       </c>
     </row>
     <row r="125" spans="1:15">
@@ -7542,37 +7542,37 @@
         <v>552</v>
       </c>
       <c r="C125">
-        <v>187.3</v>
+        <v>3.47</v>
       </c>
       <c r="D125">
-        <v>1.68</v>
+        <v>0.58</v>
       </c>
       <c r="E125">
-        <v>-10.75</v>
+        <v>-74.19</v>
       </c>
       <c r="F125">
-        <v>36.82</v>
+        <v>54.51</v>
       </c>
       <c r="G125">
-        <v>-0.3</v>
+        <v>0.02</v>
       </c>
       <c r="J125">
-        <v>222.83</v>
+        <v>3.29</v>
       </c>
       <c r="K125">
-        <v>241.72</v>
+        <v>3.29</v>
       </c>
       <c r="L125">
-        <v>214.92</v>
+        <v>3.4</v>
       </c>
       <c r="M125">
-        <v>217.43</v>
+        <v>3.29</v>
       </c>
       <c r="N125">
-        <v>234.9</v>
+        <v>3.29</v>
       </c>
       <c r="O125">
-        <v>219.95</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="126" spans="1:15">
@@ -7583,37 +7583,37 @@
         <v>552</v>
       </c>
       <c r="C126">
-        <v>85.09999999999999</v>
+        <v>187.3</v>
       </c>
       <c r="D126">
-        <v>6.37</v>
+        <v>1.68</v>
       </c>
       <c r="E126">
-        <v>-49.11</v>
+        <v>-10.75</v>
       </c>
       <c r="F126">
-        <v>69.98</v>
+        <v>36.82</v>
       </c>
       <c r="G126">
-        <v>0.63</v>
+        <v>-0.3</v>
       </c>
       <c r="J126">
-        <v>69.01000000000001</v>
+        <v>222.83</v>
       </c>
       <c r="K126">
-        <v>73.31</v>
+        <v>241.72</v>
       </c>
       <c r="L126">
-        <v>74.8</v>
+        <v>214.92</v>
       </c>
       <c r="M126">
-        <v>70.48</v>
+        <v>217.43</v>
       </c>
       <c r="N126">
-        <v>74.06999999999999</v>
+        <v>234.9</v>
       </c>
       <c r="O126">
-        <v>75.05</v>
+        <v>219.95</v>
       </c>
     </row>
     <row r="127" spans="1:15">
@@ -7624,37 +7624,37 @@
         <v>552</v>
       </c>
       <c r="C127">
-        <v>122.4</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D127">
-        <v>0.41</v>
+        <v>6.37</v>
       </c>
       <c r="E127">
-        <v>-80.04000000000001</v>
+        <v>-49.11</v>
       </c>
       <c r="F127">
-        <v>42.94</v>
+        <v>69.98</v>
       </c>
       <c r="G127">
-        <v>-0.57</v>
+        <v>0.63</v>
       </c>
       <c r="J127">
-        <v>126.77</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="K127">
-        <v>132.04</v>
+        <v>73.31</v>
       </c>
       <c r="L127">
-        <v>130.5</v>
+        <v>74.8</v>
       </c>
       <c r="M127">
-        <v>124.49</v>
+        <v>70.48</v>
       </c>
       <c r="N127">
-        <v>130.01</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="O127">
-        <v>132.69</v>
+        <v>75.05</v>
       </c>
     </row>
     <row r="128" spans="1:15">
@@ -7665,43 +7665,37 @@
         <v>552</v>
       </c>
       <c r="C128">
-        <v>23.7</v>
+        <v>122.4</v>
       </c>
       <c r="D128">
-        <v>1.8</v>
+        <v>0.41</v>
       </c>
       <c r="E128">
-        <v>-43.68</v>
+        <v>-80.04000000000001</v>
       </c>
       <c r="F128">
-        <v>46.97</v>
+        <v>42.94</v>
       </c>
       <c r="G128">
-        <v>0.13</v>
-      </c>
-      <c r="H128" t="s">
-        <v>558</v>
-      </c>
-      <c r="I128" t="s">
-        <v>618</v>
+        <v>-0.57</v>
       </c>
       <c r="J128">
-        <v>25.9</v>
+        <v>126.77</v>
       </c>
       <c r="K128">
-        <v>26.2</v>
+        <v>132.04</v>
       </c>
       <c r="L128">
-        <v>27.56</v>
+        <v>130.5</v>
       </c>
       <c r="M128">
-        <v>26.04</v>
+        <v>124.49</v>
       </c>
       <c r="N128">
-        <v>26.91</v>
+        <v>130.01</v>
       </c>
       <c r="O128">
-        <v>23.39</v>
+        <v>132.69</v>
       </c>
     </row>
     <row r="129" spans="1:15">
@@ -7712,43 +7706,43 @@
         <v>552</v>
       </c>
       <c r="C129">
-        <v>30.62</v>
+        <v>23.7</v>
       </c>
       <c r="D129">
-        <v>5.22</v>
+        <v>1.8</v>
       </c>
       <c r="E129">
-        <v>16.51</v>
+        <v>-43.68</v>
       </c>
       <c r="F129">
-        <v>42.95</v>
+        <v>46.97</v>
       </c>
       <c r="G129">
-        <v>-0.16</v>
+        <v>0.13</v>
       </c>
       <c r="H129" t="s">
-        <v>573</v>
+        <v>558</v>
       </c>
       <c r="I129" t="s">
         <v>618</v>
       </c>
       <c r="J129">
-        <v>29.13</v>
+        <v>25.9</v>
       </c>
       <c r="K129">
-        <v>36.05</v>
+        <v>26.2</v>
       </c>
       <c r="L129">
-        <v>33.69</v>
+        <v>27.56</v>
       </c>
       <c r="M129">
-        <v>26.45</v>
+        <v>26.04</v>
       </c>
       <c r="N129">
-        <v>31.89</v>
+        <v>26.91</v>
       </c>
       <c r="O129">
-        <v>36.27</v>
+        <v>23.39</v>
       </c>
     </row>
     <row r="130" spans="1:15">
@@ -7759,37 +7753,43 @@
         <v>552</v>
       </c>
       <c r="C130">
-        <v>28.86</v>
+        <v>30.62</v>
       </c>
       <c r="D130">
-        <v>-0.55</v>
+        <v>5.22</v>
       </c>
       <c r="E130">
-        <v>-70</v>
+        <v>16.51</v>
       </c>
       <c r="F130">
-        <v>42.11</v>
+        <v>42.95</v>
       </c>
       <c r="G130">
-        <v>0.01</v>
+        <v>-0.16</v>
+      </c>
+      <c r="H130" t="s">
+        <v>573</v>
+      </c>
+      <c r="I130" t="s">
+        <v>618</v>
       </c>
       <c r="J130">
-        <v>30.09</v>
+        <v>29.13</v>
       </c>
       <c r="K130">
-        <v>30.46</v>
+        <v>36.05</v>
       </c>
       <c r="L130">
-        <v>31.27</v>
+        <v>33.69</v>
       </c>
       <c r="M130">
-        <v>30.15</v>
+        <v>26.45</v>
       </c>
       <c r="N130">
-        <v>31.11</v>
+        <v>31.89</v>
       </c>
       <c r="O130">
-        <v>29.06</v>
+        <v>36.27</v>
       </c>
     </row>
     <row r="131" spans="1:15">
@@ -7800,37 +7800,37 @@
         <v>552</v>
       </c>
       <c r="C131">
-        <v>5.82</v>
+        <v>28.86</v>
       </c>
       <c r="D131">
-        <v>0.34</v>
+        <v>-0.55</v>
       </c>
       <c r="E131">
-        <v>-65.98</v>
+        <v>-70</v>
       </c>
       <c r="F131">
-        <v>42.91</v>
+        <v>42.11</v>
       </c>
       <c r="G131">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="J131">
-        <v>7.05</v>
+        <v>30.09</v>
       </c>
       <c r="K131">
-        <v>6.66</v>
+        <v>30.46</v>
       </c>
       <c r="L131">
-        <v>6.07</v>
+        <v>31.27</v>
       </c>
       <c r="M131">
-        <v>7.02</v>
+        <v>30.15</v>
       </c>
       <c r="N131">
-        <v>6.12</v>
+        <v>31.11</v>
       </c>
       <c r="O131">
-        <v>5.78</v>
+        <v>29.06</v>
       </c>
     </row>
     <row r="132" spans="1:15">
@@ -7841,37 +7841,37 @@
         <v>552</v>
       </c>
       <c r="C132">
-        <v>15.4</v>
+        <v>5.82</v>
       </c>
       <c r="D132">
-        <v>0.98</v>
+        <v>0.34</v>
       </c>
       <c r="E132">
-        <v>-54.01</v>
+        <v>-65.98</v>
       </c>
       <c r="F132">
-        <v>74.18000000000001</v>
+        <v>42.91</v>
       </c>
       <c r="G132">
-        <v>0.43</v>
+        <v>0.02</v>
       </c>
       <c r="J132">
-        <v>12.43</v>
+        <v>7.05</v>
       </c>
       <c r="K132">
-        <v>12.56</v>
+        <v>6.66</v>
       </c>
       <c r="L132">
-        <v>12.97</v>
+        <v>6.07</v>
       </c>
       <c r="M132">
-        <v>12.43</v>
+        <v>7.02</v>
       </c>
       <c r="N132">
-        <v>12.72</v>
+        <v>6.12</v>
       </c>
       <c r="O132">
-        <v>13.15</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="133" spans="1:15">
@@ -7882,37 +7882,37 @@
         <v>552</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>15.4</v>
       </c>
       <c r="D133">
-        <v>-0.5</v>
+        <v>0.98</v>
       </c>
       <c r="E133">
-        <v>-53.9</v>
+        <v>-54.01</v>
       </c>
       <c r="F133">
-        <v>36.45</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="G133">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="J133">
-        <v>2.28</v>
+        <v>12.43</v>
       </c>
       <c r="K133">
-        <v>2.25</v>
+        <v>12.56</v>
       </c>
       <c r="L133">
-        <v>2.14</v>
+        <v>12.97</v>
       </c>
       <c r="M133">
-        <v>2.28</v>
+        <v>12.43</v>
       </c>
       <c r="N133">
-        <v>2.23</v>
+        <v>12.72</v>
       </c>
       <c r="O133">
-        <v>2.04</v>
+        <v>13.15</v>
       </c>
     </row>
     <row r="134" spans="1:15">
@@ -7923,43 +7923,37 @@
         <v>552</v>
       </c>
       <c r="C134">
-        <v>8.42</v>
+        <v>2</v>
       </c>
       <c r="D134">
-        <v>0.72</v>
+        <v>-0.5</v>
       </c>
       <c r="E134">
-        <v>-3.61</v>
+        <v>-53.9</v>
       </c>
       <c r="F134">
-        <v>51.55</v>
+        <v>36.45</v>
       </c>
       <c r="G134">
-        <v>0.02</v>
-      </c>
-      <c r="H134" t="s">
-        <v>574</v>
-      </c>
-      <c r="I134" t="s">
-        <v>618</v>
+        <v>0</v>
       </c>
       <c r="J134">
-        <v>8.449999999999999</v>
+        <v>2.28</v>
       </c>
       <c r="K134">
-        <v>8.289999999999999</v>
+        <v>2.25</v>
       </c>
       <c r="L134">
-        <v>8.42</v>
+        <v>2.14</v>
       </c>
       <c r="M134">
-        <v>8.4</v>
+        <v>2.28</v>
       </c>
       <c r="N134">
-        <v>8.31</v>
+        <v>2.23</v>
       </c>
       <c r="O134">
-        <v>8.289999999999999</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="135" spans="1:15">
@@ -7970,43 +7964,43 @@
         <v>552</v>
       </c>
       <c r="C135">
-        <v>2.47</v>
+        <v>8.42</v>
       </c>
       <c r="D135">
-        <v>-0.8</v>
+        <v>0.72</v>
       </c>
       <c r="E135">
-        <v>-81.81</v>
+        <v>-3.61</v>
       </c>
       <c r="F135">
-        <v>37.54</v>
+        <v>51.55</v>
       </c>
       <c r="G135">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="H135" t="s">
-        <v>553</v>
+        <v>574</v>
       </c>
       <c r="I135" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="J135">
-        <v>2.84</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="K135">
-        <v>2.69</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="L135">
-        <v>2.49</v>
+        <v>8.42</v>
       </c>
       <c r="M135">
-        <v>2.79</v>
+        <v>8.4</v>
       </c>
       <c r="N135">
-        <v>2.52</v>
+        <v>8.31</v>
       </c>
       <c r="O135">
-        <v>2.47</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="136" spans="1:15">
@@ -8017,37 +8011,43 @@
         <v>552</v>
       </c>
       <c r="C136">
-        <v>14.45</v>
+        <v>2.47</v>
       </c>
       <c r="D136">
+        <v>-0.8</v>
+      </c>
+      <c r="E136">
+        <v>-81.81</v>
+      </c>
+      <c r="F136">
+        <v>37.54</v>
+      </c>
+      <c r="G136">
         <v>0</v>
       </c>
-      <c r="E136">
-        <v>-52.88</v>
-      </c>
-      <c r="F136">
-        <v>49.41</v>
-      </c>
-      <c r="G136">
-        <v>-0.04</v>
+      <c r="H136" t="s">
+        <v>553</v>
+      </c>
+      <c r="I136" t="s">
+        <v>616</v>
       </c>
       <c r="J136">
-        <v>14.67</v>
+        <v>2.84</v>
       </c>
       <c r="K136">
-        <v>14.63</v>
+        <v>2.69</v>
       </c>
       <c r="L136">
-        <v>14.73</v>
+        <v>2.49</v>
       </c>
       <c r="M136">
-        <v>14.56</v>
+        <v>2.79</v>
       </c>
       <c r="N136">
-        <v>14.73</v>
+        <v>2.52</v>
       </c>
       <c r="O136">
-        <v>14.6</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="137" spans="1:15">
@@ -8058,43 +8058,37 @@
         <v>552</v>
       </c>
       <c r="C137">
-        <v>37.48</v>
+        <v>14.45</v>
       </c>
       <c r="D137">
-        <v>-5.59</v>
+        <v>0</v>
       </c>
       <c r="E137">
-        <v>-77.77</v>
+        <v>-52.88</v>
       </c>
       <c r="F137">
-        <v>50.93</v>
+        <v>49.41</v>
       </c>
       <c r="G137">
-        <v>0.24</v>
-      </c>
-      <c r="H137" t="s">
-        <v>575</v>
-      </c>
-      <c r="I137" t="s">
-        <v>616</v>
+        <v>-0.04</v>
       </c>
       <c r="J137">
-        <v>37.11</v>
+        <v>14.67</v>
       </c>
       <c r="K137">
-        <v>37.82</v>
+        <v>14.63</v>
       </c>
       <c r="L137">
-        <v>37.36</v>
+        <v>14.73</v>
       </c>
       <c r="M137">
-        <v>37.03</v>
+        <v>14.56</v>
       </c>
       <c r="N137">
-        <v>37.96</v>
+        <v>14.73</v>
       </c>
       <c r="O137">
-        <v>37.25</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="138" spans="1:15">
@@ -8105,43 +8099,43 @@
         <v>552</v>
       </c>
       <c r="C138">
-        <v>12.25</v>
+        <v>37.48</v>
       </c>
       <c r="D138">
-        <v>2.6</v>
+        <v>-5.59</v>
       </c>
       <c r="E138">
-        <v>-47.54</v>
+        <v>-77.77</v>
       </c>
       <c r="F138">
-        <v>52.44</v>
+        <v>50.93</v>
       </c>
       <c r="G138">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="H138" t="s">
-        <v>555</v>
+        <v>575</v>
       </c>
       <c r="I138" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="J138">
-        <v>12.34</v>
+        <v>37.11</v>
       </c>
       <c r="K138">
-        <v>12.37</v>
+        <v>37.82</v>
       </c>
       <c r="L138">
-        <v>12.43</v>
+        <v>37.36</v>
       </c>
       <c r="M138">
-        <v>11.98</v>
+        <v>37.03</v>
       </c>
       <c r="N138">
-        <v>12.41</v>
+        <v>37.96</v>
       </c>
       <c r="O138">
-        <v>12.33</v>
+        <v>37.25</v>
       </c>
     </row>
     <row r="139" spans="1:15">
@@ -8152,37 +8146,43 @@
         <v>552</v>
       </c>
       <c r="C139">
-        <v>38.96</v>
+        <v>12.25</v>
       </c>
       <c r="D139">
-        <v>0.62</v>
+        <v>2.6</v>
       </c>
       <c r="E139">
-        <v>-66.45999999999999</v>
+        <v>-47.54</v>
       </c>
       <c r="F139">
-        <v>33.96</v>
+        <v>52.44</v>
       </c>
       <c r="G139">
-        <v>-0.13</v>
+        <v>0.03</v>
+      </c>
+      <c r="H139" t="s">
+        <v>555</v>
+      </c>
+      <c r="I139" t="s">
+        <v>618</v>
       </c>
       <c r="J139">
-        <v>46.77</v>
+        <v>12.34</v>
       </c>
       <c r="K139">
-        <v>44.93</v>
+        <v>12.37</v>
       </c>
       <c r="L139">
-        <v>41.5</v>
+        <v>12.43</v>
       </c>
       <c r="M139">
-        <v>47.67</v>
+        <v>11.98</v>
       </c>
       <c r="N139">
-        <v>45</v>
+        <v>12.41</v>
       </c>
       <c r="O139">
-        <v>42.56</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="140" spans="1:15">
